--- a/ML/DF6_futuro_3h.xlsx
+++ b/ML/DF6_futuro_3h.xlsx
@@ -444,2881 +444,2881 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46110.99930555555</v>
+        <v>46112.48611111111</v>
       </c>
       <c r="B2" t="n">
-        <v>1.6609</v>
+        <v>1.5667</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>11:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46111</v>
+        <v>46112.48680555556</v>
       </c>
       <c r="B3" t="n">
-        <v>1.66</v>
+        <v>1.5683</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46111.00069444445</v>
+        <v>46112.4875</v>
       </c>
       <c r="B4" t="n">
-        <v>1.6389</v>
+        <v>1.5703</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>11:42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46111.00138888889</v>
+        <v>46112.48819444444</v>
       </c>
       <c r="B5" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>11:43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46111.00208333333</v>
+        <v>46112.48888888889</v>
       </c>
       <c r="B6" t="n">
-        <v>1.6366</v>
+        <v>1.57</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00:03</t>
+          <t>11:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46111.00277777778</v>
+        <v>46112.48958333334</v>
       </c>
       <c r="B7" t="n">
-        <v>1.6387</v>
+        <v>1.57</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00:04</t>
+          <t>11:45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46111.00347222222</v>
+        <v>46112.49027777778</v>
       </c>
       <c r="B8" t="n">
-        <v>1.6366</v>
+        <v>1.57</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>11:46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46111.00416666667</v>
+        <v>46112.49097222222</v>
       </c>
       <c r="B9" t="n">
-        <v>1.6365</v>
+        <v>1.5701</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00:06</t>
+          <t>11:47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46111.00486111111</v>
+        <v>46112.49166666667</v>
       </c>
       <c r="B10" t="n">
-        <v>1.6366</v>
+        <v>1.5701</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00:07</t>
+          <t>11:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46111.00555555556</v>
+        <v>46112.49236111111</v>
       </c>
       <c r="B11" t="n">
-        <v>1.6368</v>
+        <v>1.5765</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>11:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46111.00625</v>
+        <v>46112.49305555555</v>
       </c>
       <c r="B12" t="n">
-        <v>1.6369</v>
+        <v>1.58</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00:09</t>
+          <t>11:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46111.00694444445</v>
+        <v>46112.49375</v>
       </c>
       <c r="B13" t="n">
-        <v>1.6368</v>
+        <v>1.58</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>11:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46111.00763888889</v>
+        <v>46112.49444444444</v>
       </c>
       <c r="B14" t="n">
-        <v>1.6377</v>
+        <v>1.5801</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00:11</t>
+          <t>11:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46111.00833333333</v>
+        <v>46112.49513888889</v>
       </c>
       <c r="B15" t="n">
-        <v>1.6381</v>
+        <v>1.58</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00:12</t>
+          <t>11:53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46111.00902777778</v>
+        <v>46112.49583333333</v>
       </c>
       <c r="B16" t="n">
-        <v>1.6312</v>
+        <v>1.5867</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>11:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46111.00972222222</v>
+        <v>46112.49652777778</v>
       </c>
       <c r="B17" t="n">
-        <v>1.629</v>
+        <v>1.5898</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00:14</t>
+          <t>11:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46111.01041666666</v>
+        <v>46112.49722222222</v>
       </c>
       <c r="B18" t="n">
-        <v>1.6273</v>
+        <v>1.5904</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>11:56</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46111.01111111111</v>
+        <v>46112.49791666667</v>
       </c>
       <c r="B19" t="n">
-        <v>1.6219</v>
+        <v>1.5905</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>11:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46111.01180555556</v>
+        <v>46112.49861111111</v>
       </c>
       <c r="B20" t="n">
-        <v>1.62</v>
+        <v>1.5902</v>
       </c>
       <c r="C20" t="n">
         <v>19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>11:58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46111.0125</v>
+        <v>46112.49930555555</v>
       </c>
       <c r="B21" t="n">
-        <v>1.62</v>
+        <v>1.5903</v>
       </c>
       <c r="C21" t="n">
         <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00:18</t>
+          <t>11:59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46111.01319444444</v>
+        <v>46112.5</v>
       </c>
       <c r="B22" t="n">
-        <v>1.62</v>
+        <v>1.5903</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00:19</t>
+          <t>12:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46111.01388888889</v>
+        <v>46112.50069444445</v>
       </c>
       <c r="B23" t="n">
-        <v>1.62</v>
+        <v>1.5903</v>
       </c>
       <c r="C23" t="n">
         <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00:20</t>
+          <t>12:01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46111.01458333333</v>
+        <v>46112.50138888889</v>
       </c>
       <c r="B24" t="n">
-        <v>1.6187</v>
+        <v>1.5903</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00:21</t>
+          <t>12:02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46111.01527777778</v>
+        <v>46112.50208333333</v>
       </c>
       <c r="B25" t="n">
-        <v>1.6128</v>
+        <v>1.5937</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00:22</t>
+          <t>12:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46111.01597222222</v>
+        <v>46112.50277777778</v>
       </c>
       <c r="B26" t="n">
-        <v>1.6095</v>
+        <v>1.5989</v>
       </c>
       <c r="C26" t="n">
         <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00:23</t>
+          <t>12:04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46111.01666666667</v>
+        <v>46112.50347222222</v>
       </c>
       <c r="B27" t="n">
-        <v>1.6083</v>
+        <v>1.6</v>
       </c>
       <c r="C27" t="n">
         <v>26</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>00:24</t>
+          <t>12:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46111.01736111111</v>
+        <v>46112.50416666667</v>
       </c>
       <c r="B28" t="n">
-        <v>1.6094</v>
+        <v>1.6</v>
       </c>
       <c r="C28" t="n">
         <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00:25</t>
+          <t>12:06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46111.01805555556</v>
+        <v>46112.50486111111</v>
       </c>
       <c r="B29" t="n">
-        <v>1.6096</v>
+        <v>1.6</v>
       </c>
       <c r="C29" t="n">
         <v>28</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00:26</t>
+          <t>12:07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46111.01875</v>
+        <v>46112.50555555556</v>
       </c>
       <c r="B30" t="n">
-        <v>1.6096</v>
+        <v>1.6</v>
       </c>
       <c r="C30" t="n">
         <v>29</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>00:27</t>
+          <t>12:08</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46111.01944444444</v>
+        <v>46112.50625</v>
       </c>
       <c r="B31" t="n">
-        <v>1.6096</v>
+        <v>1.6</v>
       </c>
       <c r="C31" t="n">
         <v>30</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00:28</t>
+          <t>12:09</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46111.02013888889</v>
+        <v>46112.50694444445</v>
       </c>
       <c r="B32" t="n">
-        <v>1.6096</v>
+        <v>1.6</v>
       </c>
       <c r="C32" t="n">
         <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>00:29</t>
+          <t>12:10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46111.02083333334</v>
+        <v>46112.50763888889</v>
       </c>
       <c r="B33" t="n">
-        <v>1.6092</v>
+        <v>1.6</v>
       </c>
       <c r="C33" t="n">
         <v>32</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>12:11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46111.02152777778</v>
+        <v>46112.50833333333</v>
       </c>
       <c r="B34" t="n">
-        <v>1.6097</v>
+        <v>1.6026</v>
       </c>
       <c r="C34" t="n">
         <v>33</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>00:31</t>
+          <t>12:12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46111.02222222222</v>
+        <v>46112.50902777778</v>
       </c>
       <c r="B35" t="n">
-        <v>1.6097</v>
+        <v>1.6067</v>
       </c>
       <c r="C35" t="n">
         <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>00:32</t>
+          <t>12:13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46111.02291666667</v>
+        <v>46112.50972222222</v>
       </c>
       <c r="B36" t="n">
-        <v>1.6098</v>
+        <v>1.6069</v>
       </c>
       <c r="C36" t="n">
         <v>35</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>12:14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46111.02361111111</v>
+        <v>46112.51041666666</v>
       </c>
       <c r="B37" t="n">
-        <v>1.6033</v>
+        <v>1.6069</v>
       </c>
       <c r="C37" t="n">
         <v>36</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>00:34</t>
+          <t>12:15</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46111.02430555555</v>
+        <v>46112.51111111111</v>
       </c>
       <c r="B38" t="n">
-        <v>1.6023</v>
+        <v>1.6069</v>
       </c>
       <c r="C38" t="n">
         <v>37</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00:35</t>
+          <t>12:16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46111.025</v>
+        <v>46112.51180555556</v>
       </c>
       <c r="B39" t="n">
-        <v>1.5973</v>
+        <v>1.6073</v>
       </c>
       <c r="C39" t="n">
         <v>38</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>12:17</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46111.02569444444</v>
+        <v>46112.5125</v>
       </c>
       <c r="B40" t="n">
-        <v>1.5985</v>
+        <v>1.6075</v>
       </c>
       <c r="C40" t="n">
         <v>39</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>00:37</t>
+          <t>12:18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46111.02638888889</v>
+        <v>46112.51319444444</v>
       </c>
       <c r="B41" t="n">
-        <v>1.5964</v>
+        <v>1.6082</v>
       </c>
       <c r="C41" t="n">
         <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>00:38</t>
+          <t>12:19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46111.02708333333</v>
+        <v>46112.51388888889</v>
       </c>
       <c r="B42" t="n">
-        <v>1.5956</v>
+        <v>1.6109</v>
       </c>
       <c r="C42" t="n">
         <v>41</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>00:39</t>
+          <t>12:20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46111.02777777778</v>
+        <v>46112.51458333333</v>
       </c>
       <c r="B43" t="n">
-        <v>1.5962</v>
+        <v>1.61</v>
       </c>
       <c r="C43" t="n">
         <v>42</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>12:21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46111.02847222222</v>
+        <v>46112.51527777778</v>
       </c>
       <c r="B44" t="n">
-        <v>1.5965</v>
+        <v>1.6101</v>
       </c>
       <c r="C44" t="n">
         <v>43</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>00:41</t>
+          <t>12:22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46111.02916666667</v>
+        <v>46112.51597222222</v>
       </c>
       <c r="B45" t="n">
-        <v>1.5927</v>
+        <v>1.6103</v>
       </c>
       <c r="C45" t="n">
         <v>44</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>00:42</t>
+          <t>12:23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46111.02986111111</v>
+        <v>46112.51666666667</v>
       </c>
       <c r="B46" t="n">
-        <v>1.592</v>
+        <v>1.6105</v>
       </c>
       <c r="C46" t="n">
         <v>45</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00:43</t>
+          <t>12:24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46111.03055555555</v>
+        <v>46112.51736111111</v>
       </c>
       <c r="B47" t="n">
-        <v>1.59</v>
+        <v>1.6102</v>
       </c>
       <c r="C47" t="n">
         <v>46</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>00:44</t>
+          <t>12:25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46111.03125</v>
+        <v>46112.51805555556</v>
       </c>
       <c r="B48" t="n">
-        <v>1.5885</v>
+        <v>1.6102</v>
       </c>
       <c r="C48" t="n">
         <v>47</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>12:26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46111.03194444445</v>
+        <v>46112.51875</v>
       </c>
       <c r="B49" t="n">
-        <v>1.5846</v>
+        <v>1.6119</v>
       </c>
       <c r="C49" t="n">
         <v>48</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00:46</t>
+          <t>12:27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46111.03263888889</v>
+        <v>46112.51944444444</v>
       </c>
       <c r="B50" t="n">
-        <v>1.5834</v>
+        <v>1.6149</v>
       </c>
       <c r="C50" t="n">
         <v>49</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>00:47</t>
+          <t>12:28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46111.03333333333</v>
+        <v>46112.52013888889</v>
       </c>
       <c r="B51" t="n">
-        <v>1.5814</v>
+        <v>1.611</v>
       </c>
       <c r="C51" t="n">
         <v>50</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00:48</t>
+          <t>12:29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46111.03402777778</v>
+        <v>46112.52083333334</v>
       </c>
       <c r="B52" t="n">
-        <v>1.5799</v>
+        <v>1.6154</v>
       </c>
       <c r="C52" t="n">
         <v>51</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00:49</t>
+          <t>12:30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46111.03472222222</v>
+        <v>46112.52152777778</v>
       </c>
       <c r="B53" t="n">
-        <v>1.58</v>
+        <v>1.6238</v>
       </c>
       <c r="C53" t="n">
         <v>52</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00:50</t>
+          <t>12:31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46111.03541666667</v>
+        <v>46112.52222222222</v>
       </c>
       <c r="B54" t="n">
-        <v>1.578</v>
+        <v>1.6231</v>
       </c>
       <c r="C54" t="n">
         <v>53</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>00:51</t>
+          <t>12:32</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46111.03611111111</v>
+        <v>46112.52291666667</v>
       </c>
       <c r="B55" t="n">
-        <v>1.5723</v>
+        <v>1.6241</v>
       </c>
       <c r="C55" t="n">
         <v>54</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>00:52</t>
+          <t>12:33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46111.03680555556</v>
+        <v>46112.52361111111</v>
       </c>
       <c r="B56" t="n">
-        <v>1.5676</v>
+        <v>1.6237</v>
       </c>
       <c r="C56" t="n">
         <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>00:53</t>
+          <t>12:34</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46111.0375</v>
+        <v>46112.52430555555</v>
       </c>
       <c r="B57" t="n">
-        <v>1.5625</v>
+        <v>1.6235</v>
       </c>
       <c r="C57" t="n">
         <v>56</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00:54</t>
+          <t>12:35</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46111.03819444445</v>
+        <v>46112.525</v>
       </c>
       <c r="B58" t="n">
-        <v>1.5599</v>
+        <v>1.6237</v>
       </c>
       <c r="C58" t="n">
         <v>57</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>12:36</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46111.03888888889</v>
+        <v>46112.52569444444</v>
       </c>
       <c r="B59" t="n">
-        <v>1.5567</v>
+        <v>1.6257</v>
       </c>
       <c r="C59" t="n">
         <v>58</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>00:56</t>
+          <t>12:37</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46111.03958333333</v>
+        <v>46112.52638888889</v>
       </c>
       <c r="B60" t="n">
-        <v>1.5534</v>
+        <v>1.627</v>
       </c>
       <c r="C60" t="n">
         <v>59</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>00:57</t>
+          <t>12:38</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46111.04027777778</v>
+        <v>46112.52708333333</v>
       </c>
       <c r="B61" t="n">
-        <v>1.5517</v>
+        <v>1.6259</v>
       </c>
       <c r="C61" t="n">
         <v>60</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>00:58</t>
+          <t>12:39</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46111.04097222222</v>
+        <v>46112.52777777778</v>
       </c>
       <c r="B62" t="n">
-        <v>1.5464</v>
+        <v>1.6254</v>
       </c>
       <c r="C62" t="n">
         <v>61</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>00:59</t>
+          <t>12:40</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46111.04166666666</v>
+        <v>46112.52847222222</v>
       </c>
       <c r="B63" t="n">
-        <v>1.5465</v>
+        <v>1.6261</v>
       </c>
       <c r="C63" t="n">
         <v>62</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>12:41</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46111.04236111111</v>
+        <v>46112.52916666667</v>
       </c>
       <c r="B64" t="n">
-        <v>1.5493</v>
+        <v>1.6268</v>
       </c>
       <c r="C64" t="n">
         <v>63</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>01:01</t>
+          <t>12:42</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46111.04305555556</v>
+        <v>46112.52986111111</v>
       </c>
       <c r="B65" t="n">
-        <v>1.5493</v>
+        <v>1.6267</v>
       </c>
       <c r="C65" t="n">
         <v>64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01:02</t>
+          <t>12:43</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46111.04375</v>
+        <v>46112.53055555555</v>
       </c>
       <c r="B66" t="n">
-        <v>1.5493</v>
+        <v>1.6264</v>
       </c>
       <c r="C66" t="n">
         <v>65</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>01:03</t>
+          <t>12:44</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46111.04444444444</v>
+        <v>46112.53125</v>
       </c>
       <c r="B67" t="n">
-        <v>1.5493</v>
+        <v>1.6267</v>
       </c>
       <c r="C67" t="n">
         <v>66</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>12:45</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46111.04513888889</v>
+        <v>46112.53194444445</v>
       </c>
       <c r="B68" t="n">
-        <v>1.5486</v>
+        <v>1.6267</v>
       </c>
       <c r="C68" t="n">
         <v>67</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>12:46</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46111.04583333333</v>
+        <v>46112.53263888889</v>
       </c>
       <c r="B69" t="n">
-        <v>1.5499</v>
+        <v>1.6267</v>
       </c>
       <c r="C69" t="n">
         <v>68</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>12:47</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46111.04652777778</v>
+        <v>46112.53333333333</v>
       </c>
       <c r="B70" t="n">
-        <v>1.55</v>
+        <v>1.6266</v>
       </c>
       <c r="C70" t="n">
         <v>69</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01:07</t>
+          <t>12:48</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46111.04722222222</v>
+        <v>46112.53402777778</v>
       </c>
       <c r="B71" t="n">
-        <v>1.55</v>
+        <v>1.6264</v>
       </c>
       <c r="C71" t="n">
         <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01:08</t>
+          <t>12:49</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46111.04791666667</v>
+        <v>46112.53472222222</v>
       </c>
       <c r="B72" t="n">
-        <v>1.55</v>
+        <v>1.6265</v>
       </c>
       <c r="C72" t="n">
         <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01:09</t>
+          <t>12:50</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46111.04861111111</v>
+        <v>46112.53541666667</v>
       </c>
       <c r="B73" t="n">
-        <v>1.55</v>
+        <v>1.6266</v>
       </c>
       <c r="C73" t="n">
         <v>72</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>12:51</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46111.04930555556</v>
+        <v>46112.53611111111</v>
       </c>
       <c r="B74" t="n">
-        <v>1.55</v>
+        <v>1.6268</v>
       </c>
       <c r="C74" t="n">
         <v>73</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>01:11</t>
+          <t>12:52</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46111.05</v>
+        <v>46112.53680555556</v>
       </c>
       <c r="B75" t="n">
-        <v>1.5473</v>
+        <v>1.6269</v>
       </c>
       <c r="C75" t="n">
         <v>74</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>01:12</t>
+          <t>12:53</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46111.05069444444</v>
+        <v>46112.5375</v>
       </c>
       <c r="B76" t="n">
-        <v>1.5436</v>
+        <v>1.6271</v>
       </c>
       <c r="C76" t="n">
         <v>75</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>01:13</t>
+          <t>12:54</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46111.05138888889</v>
+        <v>46112.53819444445</v>
       </c>
       <c r="B77" t="n">
-        <v>1.5405</v>
+        <v>1.6281</v>
       </c>
       <c r="C77" t="n">
         <v>76</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01:14</t>
+          <t>12:55</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46111.05208333334</v>
+        <v>46112.53888888889</v>
       </c>
       <c r="B78" t="n">
-        <v>1.5394</v>
+        <v>1.6319</v>
       </c>
       <c r="C78" t="n">
         <v>77</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>12:56</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46111.05277777778</v>
+        <v>46112.53958333333</v>
       </c>
       <c r="B79" t="n">
-        <v>1.54</v>
+        <v>1.6307</v>
       </c>
       <c r="C79" t="n">
         <v>78</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>01:16</t>
+          <t>12:57</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46111.05347222222</v>
+        <v>46112.54027777778</v>
       </c>
       <c r="B80" t="n">
-        <v>1.54</v>
+        <v>1.6348</v>
       </c>
       <c r="C80" t="n">
         <v>79</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>01:17</t>
+          <t>12:58</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46111.05416666667</v>
+        <v>46112.54097222222</v>
       </c>
       <c r="B81" t="n">
-        <v>1.5399</v>
+        <v>1.6392</v>
       </c>
       <c r="C81" t="n">
         <v>80</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01:18</t>
+          <t>12:59</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46111.05486111111</v>
+        <v>46112.54166666666</v>
       </c>
       <c r="B82" t="n">
-        <v>1.5374</v>
+        <v>1.6401</v>
       </c>
       <c r="C82" t="n">
         <v>81</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01:19</t>
+          <t>13:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46111.05555555555</v>
+        <v>46112.54236111111</v>
       </c>
       <c r="B83" t="n">
-        <v>1.538</v>
+        <v>1.6449</v>
       </c>
       <c r="C83" t="n">
         <v>82</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>13:01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46111.05625</v>
+        <v>46112.54305555556</v>
       </c>
       <c r="B84" t="n">
-        <v>1.5378</v>
+        <v>1.6497</v>
       </c>
       <c r="C84" t="n">
         <v>83</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01:21</t>
+          <t>13:02</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46111.05694444444</v>
+        <v>46112.54375</v>
       </c>
       <c r="B85" t="n">
-        <v>1.538</v>
+        <v>1.6511</v>
       </c>
       <c r="C85" t="n">
         <v>84</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>01:22</t>
+          <t>13:03</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46111.05763888889</v>
+        <v>46112.54444444444</v>
       </c>
       <c r="B86" t="n">
-        <v>1.54</v>
+        <v>1.6519</v>
       </c>
       <c r="C86" t="n">
         <v>85</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>01:23</t>
+          <t>13:04</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46111.05833333333</v>
+        <v>46112.54513888889</v>
       </c>
       <c r="B87" t="n">
-        <v>1.5374</v>
+        <v>1.6514</v>
       </c>
       <c r="C87" t="n">
         <v>86</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01:24</t>
+          <t>13:05</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46111.05902777778</v>
+        <v>46112.54583333333</v>
       </c>
       <c r="B88" t="n">
-        <v>1.5313</v>
+        <v>1.651</v>
       </c>
       <c r="C88" t="n">
         <v>87</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01:25</t>
+          <t>13:06</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46111.05972222222</v>
+        <v>46112.54652777778</v>
       </c>
       <c r="B89" t="n">
-        <v>1.53</v>
+        <v>1.6512</v>
       </c>
       <c r="C89" t="n">
         <v>88</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01:26</t>
+          <t>13:07</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46111.06041666667</v>
+        <v>46112.54722222222</v>
       </c>
       <c r="B90" t="n">
-        <v>1.53</v>
+        <v>1.6545</v>
       </c>
       <c r="C90" t="n">
         <v>89</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>01:27</t>
+          <t>13:08</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46111.06111111111</v>
+        <v>46112.54791666667</v>
       </c>
       <c r="B91" t="n">
-        <v>1.5288</v>
+        <v>1.657</v>
       </c>
       <c r="C91" t="n">
         <v>90</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>01:28</t>
+          <t>13:09</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46111.06180555555</v>
+        <v>46112.54861111111</v>
       </c>
       <c r="B92" t="n">
-        <v>1.5255</v>
+        <v>1.6577</v>
       </c>
       <c r="C92" t="n">
         <v>91</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>01:29</t>
+          <t>13:10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46111.0625</v>
+        <v>46112.54930555556</v>
       </c>
       <c r="B93" t="n">
-        <v>1.5249</v>
+        <v>1.6622</v>
       </c>
       <c r="C93" t="n">
         <v>92</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>13:11</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46111.06319444445</v>
+        <v>46112.55</v>
       </c>
       <c r="B94" t="n">
-        <v>1.52</v>
+        <v>1.6601</v>
       </c>
       <c r="C94" t="n">
         <v>93</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>01:31</t>
+          <t>13:12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46111.06388888889</v>
+        <v>46112.55069444444</v>
       </c>
       <c r="B95" t="n">
-        <v>1.5183</v>
+        <v>1.6604</v>
       </c>
       <c r="C95" t="n">
         <v>94</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>01:32</t>
+          <t>13:13</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46111.06458333333</v>
+        <v>46112.55138888889</v>
       </c>
       <c r="B96" t="n">
-        <v>1.5183</v>
+        <v>1.6605</v>
       </c>
       <c r="C96" t="n">
         <v>95</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>01:33</t>
+          <t>13:14</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46111.06527777778</v>
+        <v>46112.55208333334</v>
       </c>
       <c r="B97" t="n">
-        <v>1.5183</v>
+        <v>1.66</v>
       </c>
       <c r="C97" t="n">
         <v>96</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>01:34</t>
+          <t>13:15</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46111.06597222222</v>
+        <v>46112.55277777778</v>
       </c>
       <c r="B98" t="n">
-        <v>1.5122</v>
+        <v>1.6602</v>
       </c>
       <c r="C98" t="n">
         <v>97</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>01:35</t>
+          <t>13:16</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46111.06666666667</v>
+        <v>46112.55347222222</v>
       </c>
       <c r="B99" t="n">
-        <v>1.505</v>
+        <v>1.66</v>
       </c>
       <c r="C99" t="n">
         <v>98</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>01:36</t>
+          <t>13:17</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46111.06736111111</v>
+        <v>46112.55416666667</v>
       </c>
       <c r="B100" t="n">
-        <v>1.5029</v>
+        <v>1.66</v>
       </c>
       <c r="C100" t="n">
         <v>99</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>01:37</t>
+          <t>13:18</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46111.06805555556</v>
+        <v>46112.55486111111</v>
       </c>
       <c r="B101" t="n">
-        <v>1.5026</v>
+        <v>1.6602</v>
       </c>
       <c r="C101" t="n">
         <v>100</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>13:19</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46111.06875</v>
+        <v>46112.55555555555</v>
       </c>
       <c r="B102" t="n">
-        <v>1.5026</v>
+        <v>1.6604</v>
       </c>
       <c r="C102" t="n">
         <v>101</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>01:39</t>
+          <t>13:20</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46111.06944444445</v>
+        <v>46112.55625</v>
       </c>
       <c r="B103" t="n">
-        <v>1.5026</v>
+        <v>1.6604</v>
       </c>
       <c r="C103" t="n">
         <v>102</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>13:21</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46111.07013888889</v>
+        <v>46112.55694444444</v>
       </c>
       <c r="B104" t="n">
-        <v>1.5026</v>
+        <v>1.6629</v>
       </c>
       <c r="C104" t="n">
         <v>103</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>01:41</t>
+          <t>13:22</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46111.07083333333</v>
+        <v>46112.55763888889</v>
       </c>
       <c r="B105" t="n">
-        <v>1.5007</v>
+        <v>1.6681</v>
       </c>
       <c r="C105" t="n">
         <v>104</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>01:42</t>
+          <t>13:23</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46111.07152777778</v>
+        <v>46112.55833333333</v>
       </c>
       <c r="B106" t="n">
-        <v>1.4932</v>
+        <v>1.67</v>
       </c>
       <c r="C106" t="n">
         <v>105</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>01:43</t>
+          <t>13:24</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46111.07222222222</v>
+        <v>46112.55902777778</v>
       </c>
       <c r="B107" t="n">
-        <v>1.4895</v>
+        <v>1.6708</v>
       </c>
       <c r="C107" t="n">
         <v>106</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>01:44</t>
+          <t>13:25</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46111.07291666666</v>
+        <v>46112.55972222222</v>
       </c>
       <c r="B108" t="n">
-        <v>1.4895</v>
+        <v>1.6718</v>
       </c>
       <c r="C108" t="n">
         <v>107</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>13:26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46111.07361111111</v>
+        <v>46112.56041666667</v>
       </c>
       <c r="B109" t="n">
-        <v>1.4895</v>
+        <v>1.6714</v>
       </c>
       <c r="C109" t="n">
         <v>108</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>13:27</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46111.07430555556</v>
+        <v>46112.56111111111</v>
       </c>
       <c r="B110" t="n">
-        <v>1.4893</v>
+        <v>1.6718</v>
       </c>
       <c r="C110" t="n">
         <v>109</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>01:47</t>
+          <t>13:28</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46111.075</v>
+        <v>46112.56180555555</v>
       </c>
       <c r="B111" t="n">
-        <v>1.4888</v>
+        <v>1.6747</v>
       </c>
       <c r="C111" t="n">
         <v>110</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>01:48</t>
+          <t>13:29</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46111.07569444444</v>
+        <v>46112.5625</v>
       </c>
       <c r="B112" t="n">
-        <v>1.4858</v>
+        <v>1.6761</v>
       </c>
       <c r="C112" t="n">
         <v>111</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>01:49</t>
+          <t>13:30</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46111.07638888889</v>
+        <v>46112.56319444445</v>
       </c>
       <c r="B113" t="n">
-        <v>1.4857</v>
+        <v>1.6796</v>
       </c>
       <c r="C113" t="n">
         <v>112</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>13:31</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46111.07708333333</v>
+        <v>46112.56388888889</v>
       </c>
       <c r="B114" t="n">
-        <v>1.4857</v>
+        <v>1.68</v>
       </c>
       <c r="C114" t="n">
         <v>113</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>13:32</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46111.07777777778</v>
+        <v>46112.56458333333</v>
       </c>
       <c r="B115" t="n">
-        <v>1.4857</v>
+        <v>1.6807</v>
       </c>
       <c r="C115" t="n">
         <v>114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>01:52</t>
+          <t>13:33</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46111.07847222222</v>
+        <v>46112.56527777778</v>
       </c>
       <c r="B116" t="n">
-        <v>1.49</v>
+        <v>1.6802</v>
       </c>
       <c r="C116" t="n">
         <v>115</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>01:53</t>
+          <t>13:34</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46111.07916666667</v>
+        <v>46112.56597222222</v>
       </c>
       <c r="B117" t="n">
-        <v>1.49</v>
+        <v>1.6803</v>
       </c>
       <c r="C117" t="n">
         <v>116</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>01:54</t>
+          <t>13:35</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46111.07986111111</v>
+        <v>46112.56666666667</v>
       </c>
       <c r="B118" t="n">
-        <v>1.49</v>
+        <v>1.6805</v>
       </c>
       <c r="C118" t="n">
         <v>117</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>01:55</t>
+          <t>13:36</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46111.08055555556</v>
+        <v>46112.56736111111</v>
       </c>
       <c r="B119" t="n">
-        <v>1.4865</v>
+        <v>1.6803</v>
       </c>
       <c r="C119" t="n">
         <v>118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>01:56</t>
+          <t>13:37</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46111.08125</v>
+        <v>46112.56805555556</v>
       </c>
       <c r="B120" t="n">
-        <v>1.4844</v>
+        <v>1.6802</v>
       </c>
       <c r="C120" t="n">
         <v>119</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>01:57</t>
+          <t>13:38</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46111.08194444444</v>
+        <v>46112.56875</v>
       </c>
       <c r="B121" t="n">
-        <v>1.4798</v>
+        <v>1.6802</v>
       </c>
       <c r="C121" t="n">
         <v>120</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>01:58</t>
+          <t>13:39</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46111.08263888889</v>
+        <v>46112.56944444445</v>
       </c>
       <c r="B122" t="n">
-        <v>1.4796</v>
+        <v>1.6802</v>
       </c>
       <c r="C122" t="n">
         <v>121</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>01:59</t>
+          <t>13:40</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46111.08333333334</v>
+        <v>46112.57013888889</v>
       </c>
       <c r="B123" t="n">
-        <v>1.4795</v>
+        <v>1.6804</v>
       </c>
       <c r="C123" t="n">
         <v>122</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>13:41</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111.08402777778</v>
+        <v>46112.57083333333</v>
       </c>
       <c r="B124" t="n">
-        <v>1.4791</v>
+        <v>1.6807</v>
       </c>
       <c r="C124" t="n">
         <v>123</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>13:42</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111.08472222222</v>
+        <v>46112.57152777778</v>
       </c>
       <c r="B125" t="n">
-        <v>1.48</v>
+        <v>1.6801</v>
       </c>
       <c r="C125" t="n">
         <v>124</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>02:02</t>
+          <t>13:43</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111.08541666667</v>
+        <v>46112.57222222222</v>
       </c>
       <c r="B126" t="n">
-        <v>1.48</v>
+        <v>1.6809</v>
       </c>
       <c r="C126" t="n">
         <v>125</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>02:03</t>
+          <t>13:44</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111.08611111111</v>
+        <v>46112.57291666666</v>
       </c>
       <c r="B127" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="C127" t="n">
         <v>126</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>02:04</t>
+          <t>13:45</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111.08680555555</v>
+        <v>46112.57361111111</v>
       </c>
       <c r="B128" t="n">
-        <v>1.4799</v>
+        <v>1.6791</v>
       </c>
       <c r="C128" t="n">
         <v>127</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>13:46</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111.0875</v>
+        <v>46112.57430555556</v>
       </c>
       <c r="B129" t="n">
-        <v>1.48</v>
+        <v>1.676</v>
       </c>
       <c r="C129" t="n">
         <v>128</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>02:06</t>
+          <t>13:47</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46111.08819444444</v>
+        <v>46112.575</v>
       </c>
       <c r="B130" t="n">
-        <v>1.4799</v>
+        <v>1.6735</v>
       </c>
       <c r="C130" t="n">
         <v>129</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>02:07</t>
+          <t>13:48</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46111.08888888889</v>
+        <v>46112.57569444444</v>
       </c>
       <c r="B131" t="n">
-        <v>1.4792</v>
+        <v>1.6718</v>
       </c>
       <c r="C131" t="n">
         <v>130</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>02:08</t>
+          <t>13:49</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46111.08958333333</v>
+        <v>46112.57638888889</v>
       </c>
       <c r="B132" t="n">
-        <v>1.4785</v>
+        <v>1.6683</v>
       </c>
       <c r="C132" t="n">
         <v>131</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>02:09</t>
+          <t>13:50</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111.09027777778</v>
+        <v>46112.57708333333</v>
       </c>
       <c r="B133" t="n">
-        <v>1.4804</v>
+        <v>1.669</v>
       </c>
       <c r="C133" t="n">
         <v>132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>13:51</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46111.09097222222</v>
+        <v>46112.57777777778</v>
       </c>
       <c r="B134" t="n">
-        <v>1.4806</v>
+        <v>1.664</v>
       </c>
       <c r="C134" t="n">
         <v>133</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>02:11</t>
+          <t>13:52</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111.09166666667</v>
+        <v>46112.57847222222</v>
       </c>
       <c r="B135" t="n">
-        <v>1.4793</v>
+        <v>1.664</v>
       </c>
       <c r="C135" t="n">
         <v>134</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>02:12</t>
+          <t>13:53</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46111.09236111111</v>
+        <v>46112.57916666667</v>
       </c>
       <c r="B136" t="n">
-        <v>1.4789</v>
+        <v>1.6603</v>
       </c>
       <c r="C136" t="n">
         <v>135</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>02:13</t>
+          <t>13:54</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111.09305555555</v>
+        <v>46112.57986111111</v>
       </c>
       <c r="B137" t="n">
-        <v>1.4798</v>
+        <v>1.6579</v>
       </c>
       <c r="C137" t="n">
         <v>136</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>13:55</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46111.09375</v>
+        <v>46112.58055555556</v>
       </c>
       <c r="B138" t="n">
-        <v>1.4833</v>
+        <v>1.6556</v>
       </c>
       <c r="C138" t="n">
         <v>137</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>13:56</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111.09444444445</v>
+        <v>46112.58125</v>
       </c>
       <c r="B139" t="n">
-        <v>1.4871</v>
+        <v>1.6494</v>
       </c>
       <c r="C139" t="n">
         <v>138</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>02:16</t>
+          <t>13:57</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111.09513888889</v>
+        <v>46112.58194444444</v>
       </c>
       <c r="B140" t="n">
-        <v>1.4942</v>
+        <v>1.6442</v>
       </c>
       <c r="C140" t="n">
         <v>139</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>02:17</t>
+          <t>13:58</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111.09583333333</v>
+        <v>46112.58263888889</v>
       </c>
       <c r="B141" t="n">
-        <v>1.4903</v>
+        <v>1.6423</v>
       </c>
       <c r="C141" t="n">
         <v>140</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>02:18</t>
+          <t>13:59</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46111.09652777778</v>
+        <v>46112.58333333334</v>
       </c>
       <c r="B142" t="n">
-        <v>1.495</v>
+        <v>1.638</v>
       </c>
       <c r="C142" t="n">
         <v>141</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>02:19</t>
+          <t>14:00</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111.09722222222</v>
+        <v>46112.58402777778</v>
       </c>
       <c r="B143" t="n">
-        <v>1.498</v>
+        <v>1.6374</v>
       </c>
       <c r="C143" t="n">
         <v>142</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>02:20</t>
+          <t>14:01</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46111.09791666667</v>
+        <v>46112.58472222222</v>
       </c>
       <c r="B144" t="n">
-        <v>1.5068</v>
+        <v>1.6331</v>
       </c>
       <c r="C144" t="n">
         <v>143</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>02:21</t>
+          <t>14:02</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46111.09861111111</v>
+        <v>46112.58541666667</v>
       </c>
       <c r="B145" t="n">
-        <v>1.51</v>
+        <v>1.6367</v>
       </c>
       <c r="C145" t="n">
         <v>144</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>02:22</t>
+          <t>14:03</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46111.09930555556</v>
+        <v>46112.58611111111</v>
       </c>
       <c r="B146" t="n">
-        <v>1.5104</v>
+        <v>1.633</v>
       </c>
       <c r="C146" t="n">
         <v>145</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>02:23</t>
+          <t>14:04</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46111.1</v>
+        <v>46112.58680555555</v>
       </c>
       <c r="B147" t="n">
-        <v>1.5127</v>
+        <v>1.6366</v>
       </c>
       <c r="C147" t="n">
         <v>146</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>02:24</t>
+          <t>14:05</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46111.10069444445</v>
+        <v>46112.5875</v>
       </c>
       <c r="B148" t="n">
-        <v>1.5129</v>
+        <v>1.6328</v>
       </c>
       <c r="C148" t="n">
         <v>147</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>02:25</t>
+          <t>14:06</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46111.10138888889</v>
+        <v>46112.58819444444</v>
       </c>
       <c r="B149" t="n">
-        <v>1.5129</v>
+        <v>1.6365</v>
       </c>
       <c r="C149" t="n">
         <v>148</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>02:26</t>
+          <t>14:07</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46111.10208333333</v>
+        <v>46112.58888888889</v>
       </c>
       <c r="B150" t="n">
-        <v>1.519</v>
+        <v>1.6316</v>
       </c>
       <c r="C150" t="n">
         <v>149</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>02:27</t>
+          <t>14:08</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46111.10277777778</v>
+        <v>46112.58958333333</v>
       </c>
       <c r="B151" t="n">
-        <v>1.5216</v>
+        <v>1.6232</v>
       </c>
       <c r="C151" t="n">
         <v>150</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>02:28</t>
+          <t>14:09</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46111.10347222222</v>
+        <v>46112.59027777778</v>
       </c>
       <c r="B152" t="n">
-        <v>1.5266</v>
+        <v>1.6231</v>
       </c>
       <c r="C152" t="n">
         <v>151</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>02:29</t>
+          <t>14:10</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46111.10416666666</v>
+        <v>46112.59097222222</v>
       </c>
       <c r="B153" t="n">
-        <v>1.5326</v>
+        <v>1.6169</v>
       </c>
       <c r="C153" t="n">
         <v>152</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>14:11</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46111.10486111111</v>
+        <v>46112.59166666667</v>
       </c>
       <c r="B154" t="n">
-        <v>1.5374</v>
+        <v>1.62</v>
       </c>
       <c r="C154" t="n">
         <v>153</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>02:31</t>
+          <t>14:12</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46111.10555555556</v>
+        <v>46112.59236111111</v>
       </c>
       <c r="B155" t="n">
-        <v>1.5421</v>
+        <v>1.615</v>
       </c>
       <c r="C155" t="n">
         <v>154</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>02:32</t>
+          <t>14:13</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46111.10625</v>
+        <v>46112.59305555555</v>
       </c>
       <c r="B156" t="n">
-        <v>1.5421</v>
+        <v>1.6094</v>
       </c>
       <c r="C156" t="n">
         <v>155</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>02:33</t>
+          <t>14:14</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46111.10694444444</v>
+        <v>46112.59375</v>
       </c>
       <c r="B157" t="n">
-        <v>1.5425</v>
+        <v>1.6089</v>
       </c>
       <c r="C157" t="n">
         <v>156</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>02:34</t>
+          <t>14:15</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46111.10763888889</v>
+        <v>46112.59444444445</v>
       </c>
       <c r="B158" t="n">
-        <v>1.5485</v>
+        <v>1.6067</v>
       </c>
       <c r="C158" t="n">
         <v>157</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>02:35</t>
+          <t>14:16</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46111.10833333333</v>
+        <v>46112.59513888889</v>
       </c>
       <c r="B159" t="n">
-        <v>1.5508</v>
+        <v>1.6047</v>
       </c>
       <c r="C159" t="n">
         <v>158</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>02:36</t>
+          <t>14:17</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46111.10902777778</v>
+        <v>46112.59583333333</v>
       </c>
       <c r="B160" t="n">
-        <v>1.5524</v>
+        <v>1.6019</v>
       </c>
       <c r="C160" t="n">
         <v>159</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>14:18</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46111.10972222222</v>
+        <v>46112.59652777778</v>
       </c>
       <c r="B161" t="n">
-        <v>1.5525</v>
+        <v>1.5961</v>
       </c>
       <c r="C161" t="n">
         <v>160</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>02:38</t>
+          <t>14:19</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46111.11041666667</v>
+        <v>46112.59722222222</v>
       </c>
       <c r="B162" t="n">
-        <v>1.5523</v>
+        <v>1.5956</v>
       </c>
       <c r="C162" t="n">
         <v>161</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>02:39</t>
+          <t>14:20</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46111.11111111111</v>
+        <v>46112.59791666667</v>
       </c>
       <c r="B163" t="n">
-        <v>1.5523</v>
+        <v>1.5948</v>
       </c>
       <c r="C163" t="n">
         <v>162</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>02:40</t>
+          <t>14:21</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46111.11180555556</v>
+        <v>46112.59861111111</v>
       </c>
       <c r="B164" t="n">
-        <v>1.5528</v>
+        <v>1.5968</v>
       </c>
       <c r="C164" t="n">
         <v>163</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>02:41</t>
+          <t>14:22</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46111.1125</v>
+        <v>46112.59930555556</v>
       </c>
       <c r="B165" t="n">
-        <v>1.5579</v>
+        <v>1.5964</v>
       </c>
       <c r="C165" t="n">
         <v>164</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>02:42</t>
+          <t>14:23</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46111.11319444444</v>
+        <v>46112.6</v>
       </c>
       <c r="B166" t="n">
-        <v>1.5624</v>
+        <v>1.595</v>
       </c>
       <c r="C166" t="n">
         <v>165</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>02:43</t>
+          <t>14:24</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46111.11388888889</v>
+        <v>46112.60069444445</v>
       </c>
       <c r="B167" t="n">
-        <v>1.5618</v>
+        <v>1.5918</v>
       </c>
       <c r="C167" t="n">
         <v>166</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>02:44</t>
+          <t>14:25</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46111.11458333334</v>
+        <v>46112.60138888889</v>
       </c>
       <c r="B168" t="n">
-        <v>1.5618</v>
+        <v>1.5826</v>
       </c>
       <c r="C168" t="n">
         <v>167</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>14:26</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46111.11527777778</v>
+        <v>46112.60208333333</v>
       </c>
       <c r="B169" t="n">
-        <v>1.5617</v>
+        <v>1.5855</v>
       </c>
       <c r="C169" t="n">
         <v>168</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>02:46</t>
+          <t>14:27</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46111.11597222222</v>
+        <v>46112.60277777778</v>
       </c>
       <c r="B170" t="n">
-        <v>1.562</v>
+        <v>1.5822</v>
       </c>
       <c r="C170" t="n">
         <v>169</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>02:47</t>
+          <t>14:28</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46111.11666666667</v>
+        <v>46112.60347222222</v>
       </c>
       <c r="B171" t="n">
-        <v>1.564</v>
+        <v>1.579</v>
       </c>
       <c r="C171" t="n">
         <v>170</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>02:48</t>
+          <t>14:29</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46111.11736111111</v>
+        <v>46112.60416666666</v>
       </c>
       <c r="B172" t="n">
-        <v>1.5712</v>
+        <v>1.579</v>
       </c>
       <c r="C172" t="n">
         <v>171</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>02:49</t>
+          <t>14:30</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46111.11805555555</v>
+        <v>46112.60486111111</v>
       </c>
       <c r="B173" t="n">
-        <v>1.5705</v>
+        <v>1.5759</v>
       </c>
       <c r="C173" t="n">
         <v>172</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>02:50</t>
+          <t>14:31</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46111.11875</v>
+        <v>46112.60555555556</v>
       </c>
       <c r="B174" t="n">
-        <v>1.572</v>
+        <v>1.5796</v>
       </c>
       <c r="C174" t="n">
         <v>173</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>02:51</t>
+          <t>14:32</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46111.11944444444</v>
+        <v>46112.60625</v>
       </c>
       <c r="B175" t="n">
-        <v>1.5744</v>
+        <v>1.5745</v>
       </c>
       <c r="C175" t="n">
         <v>174</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>02:52</t>
+          <t>14:33</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46111.12013888889</v>
+        <v>46112.60694444444</v>
       </c>
       <c r="B176" t="n">
-        <v>1.5808</v>
+        <v>1.576</v>
       </c>
       <c r="C176" t="n">
         <v>175</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>02:53</t>
+          <t>14:34</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46111.12083333333</v>
+        <v>46112.60763888889</v>
       </c>
       <c r="B177" t="n">
-        <v>1.5808</v>
+        <v>1.5736</v>
       </c>
       <c r="C177" t="n">
         <v>176</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>02:54</t>
+          <t>14:35</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46111.12152777778</v>
+        <v>46112.60833333333</v>
       </c>
       <c r="B178" t="n">
-        <v>1.5834</v>
+        <v>1.5729</v>
       </c>
       <c r="C178" t="n">
         <v>177</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>02:55</t>
+          <t>14:36</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46111.12222222222</v>
+        <v>46112.60902777778</v>
       </c>
       <c r="B179" t="n">
-        <v>1.5899</v>
+        <v>1.5733</v>
       </c>
       <c r="C179" t="n">
         <v>178</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>02:56</t>
+          <t>14:37</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46111.12291666667</v>
+        <v>46112.60972222222</v>
       </c>
       <c r="B180" t="n">
-        <v>1.5937</v>
+        <v>1.5746</v>
       </c>
       <c r="C180" t="n">
         <v>179</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>02:57</t>
+          <t>14:38</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46111.12361111111</v>
+        <v>46112.61041666667</v>
       </c>
       <c r="B181" t="n">
-        <v>1.6013</v>
+        <v>1.5761</v>
       </c>
       <c r="C181" t="n">
         <v>180</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>02:58</t>
+          <t>14:39</t>
         </is>
       </c>
     </row>

--- a/ML/DF6_futuro_3h.xlsx
+++ b/ML/DF6_futuro_3h.xlsx
@@ -447,7 +447,7 @@
         <v>46112.48611111111</v>
       </c>
       <c r="B2" t="n">
-        <v>1.5667</v>
+        <v>1.5664</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -463,7 +463,7 @@
         <v>46112.48680555556</v>
       </c>
       <c r="B3" t="n">
-        <v>1.5683</v>
+        <v>1.5685</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -591,7 +591,7 @@
         <v>46112.49236111111</v>
       </c>
       <c r="B11" t="n">
-        <v>1.5765</v>
+        <v>1.5766</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
@@ -671,7 +671,7 @@
         <v>46112.49583333333</v>
       </c>
       <c r="B16" t="n">
-        <v>1.5867</v>
+        <v>1.5869</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
@@ -687,7 +687,7 @@
         <v>46112.49652777778</v>
       </c>
       <c r="B17" t="n">
-        <v>1.5898</v>
+        <v>1.5895</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
@@ -703,7 +703,7 @@
         <v>46112.49722222222</v>
       </c>
       <c r="B18" t="n">
-        <v>1.5904</v>
+        <v>1.5906</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
@@ -719,7 +719,7 @@
         <v>46112.49791666667</v>
       </c>
       <c r="B19" t="n">
-        <v>1.5905</v>
+        <v>1.5908</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
@@ -815,7 +815,7 @@
         <v>46112.50208333333</v>
       </c>
       <c r="B25" t="n">
-        <v>1.5937</v>
+        <v>1.5934</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -943,7 +943,7 @@
         <v>46112.50763888889</v>
       </c>
       <c r="B33" t="n">
-        <v>1.6</v>
+        <v>1.6001</v>
       </c>
       <c r="C33" t="n">
         <v>32</v>
@@ -959,7 +959,7 @@
         <v>46112.50833333333</v>
       </c>
       <c r="B34" t="n">
-        <v>1.6026</v>
+        <v>1.6028</v>
       </c>
       <c r="C34" t="n">
         <v>33</v>
@@ -975,7 +975,7 @@
         <v>46112.50902777778</v>
       </c>
       <c r="B35" t="n">
-        <v>1.6067</v>
+        <v>1.6069</v>
       </c>
       <c r="C35" t="n">
         <v>34</v>
@@ -1007,7 +1007,7 @@
         <v>46112.51041666666</v>
       </c>
       <c r="B37" t="n">
-        <v>1.6069</v>
+        <v>1.6068</v>
       </c>
       <c r="C37" t="n">
         <v>36</v>
@@ -1039,7 +1039,7 @@
         <v>46112.51180555556</v>
       </c>
       <c r="B39" t="n">
-        <v>1.6073</v>
+        <v>1.6072</v>
       </c>
       <c r="C39" t="n">
         <v>38</v>
@@ -1055,7 +1055,7 @@
         <v>46112.5125</v>
       </c>
       <c r="B40" t="n">
-        <v>1.6075</v>
+        <v>1.6074</v>
       </c>
       <c r="C40" t="n">
         <v>39</v>
@@ -1087,7 +1087,7 @@
         <v>46112.51388888889</v>
       </c>
       <c r="B42" t="n">
-        <v>1.6109</v>
+        <v>1.611</v>
       </c>
       <c r="C42" t="n">
         <v>41</v>
@@ -1119,7 +1119,7 @@
         <v>46112.51527777778</v>
       </c>
       <c r="B44" t="n">
-        <v>1.6101</v>
+        <v>1.61</v>
       </c>
       <c r="C44" t="n">
         <v>43</v>
@@ -1135,7 +1135,7 @@
         <v>46112.51597222222</v>
       </c>
       <c r="B45" t="n">
-        <v>1.6103</v>
+        <v>1.6104</v>
       </c>
       <c r="C45" t="n">
         <v>44</v>
@@ -1151,7 +1151,7 @@
         <v>46112.51666666667</v>
       </c>
       <c r="B46" t="n">
-        <v>1.6105</v>
+        <v>1.6106</v>
       </c>
       <c r="C46" t="n">
         <v>45</v>
@@ -1167,7 +1167,7 @@
         <v>46112.51736111111</v>
       </c>
       <c r="B47" t="n">
-        <v>1.6102</v>
+        <v>1.6103</v>
       </c>
       <c r="C47" t="n">
         <v>46</v>
@@ -1183,7 +1183,7 @@
         <v>46112.51805555556</v>
       </c>
       <c r="B48" t="n">
-        <v>1.6102</v>
+        <v>1.6103</v>
       </c>
       <c r="C48" t="n">
         <v>47</v>
@@ -1215,7 +1215,7 @@
         <v>46112.51944444444</v>
       </c>
       <c r="B50" t="n">
-        <v>1.6149</v>
+        <v>1.6148</v>
       </c>
       <c r="C50" t="n">
         <v>49</v>
@@ -1231,7 +1231,7 @@
         <v>46112.52013888889</v>
       </c>
       <c r="B51" t="n">
-        <v>1.611</v>
+        <v>1.6111</v>
       </c>
       <c r="C51" t="n">
         <v>50</v>
@@ -1247,7 +1247,7 @@
         <v>46112.52083333334</v>
       </c>
       <c r="B52" t="n">
-        <v>1.6154</v>
+        <v>1.6156</v>
       </c>
       <c r="C52" t="n">
         <v>51</v>
@@ -1263,7 +1263,7 @@
         <v>46112.52152777778</v>
       </c>
       <c r="B53" t="n">
-        <v>1.6238</v>
+        <v>1.6237</v>
       </c>
       <c r="C53" t="n">
         <v>52</v>
@@ -1327,7 +1327,7 @@
         <v>46112.52430555555</v>
       </c>
       <c r="B57" t="n">
-        <v>1.6235</v>
+        <v>1.6234</v>
       </c>
       <c r="C57" t="n">
         <v>56</v>
@@ -1343,7 +1343,7 @@
         <v>46112.525</v>
       </c>
       <c r="B58" t="n">
-        <v>1.6237</v>
+        <v>1.6238</v>
       </c>
       <c r="C58" t="n">
         <v>57</v>
@@ -1359,7 +1359,7 @@
         <v>46112.52569444444</v>
       </c>
       <c r="B59" t="n">
-        <v>1.6257</v>
+        <v>1.6261</v>
       </c>
       <c r="C59" t="n">
         <v>58</v>
@@ -1375,7 +1375,7 @@
         <v>46112.52638888889</v>
       </c>
       <c r="B60" t="n">
-        <v>1.627</v>
+        <v>1.6264</v>
       </c>
       <c r="C60" t="n">
         <v>59</v>
@@ -1391,7 +1391,7 @@
         <v>46112.52708333333</v>
       </c>
       <c r="B61" t="n">
-        <v>1.6259</v>
+        <v>1.6261</v>
       </c>
       <c r="C61" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         <v>46112.52777777778</v>
       </c>
       <c r="B62" t="n">
-        <v>1.6254</v>
+        <v>1.6257</v>
       </c>
       <c r="C62" t="n">
         <v>61</v>
@@ -1423,7 +1423,7 @@
         <v>46112.52847222222</v>
       </c>
       <c r="B63" t="n">
-        <v>1.6261</v>
+        <v>1.6267</v>
       </c>
       <c r="C63" t="n">
         <v>62</v>
@@ -1439,7 +1439,7 @@
         <v>46112.52916666667</v>
       </c>
       <c r="B64" t="n">
-        <v>1.6268</v>
+        <v>1.6271</v>
       </c>
       <c r="C64" t="n">
         <v>63</v>
@@ -1455,7 +1455,7 @@
         <v>46112.52986111111</v>
       </c>
       <c r="B65" t="n">
-        <v>1.6267</v>
+        <v>1.627</v>
       </c>
       <c r="C65" t="n">
         <v>64</v>
@@ -1471,7 +1471,7 @@
         <v>46112.53055555555</v>
       </c>
       <c r="B66" t="n">
-        <v>1.6264</v>
+        <v>1.6263</v>
       </c>
       <c r="C66" t="n">
         <v>65</v>
@@ -1487,7 +1487,7 @@
         <v>46112.53125</v>
       </c>
       <c r="B67" t="n">
-        <v>1.6267</v>
+        <v>1.6269</v>
       </c>
       <c r="C67" t="n">
         <v>66</v>
@@ -1503,7 +1503,7 @@
         <v>46112.53194444445</v>
       </c>
       <c r="B68" t="n">
-        <v>1.6267</v>
+        <v>1.627</v>
       </c>
       <c r="C68" t="n">
         <v>67</v>
@@ -1519,7 +1519,7 @@
         <v>46112.53263888889</v>
       </c>
       <c r="B69" t="n">
-        <v>1.6267</v>
+        <v>1.627</v>
       </c>
       <c r="C69" t="n">
         <v>68</v>
@@ -1535,7 +1535,7 @@
         <v>46112.53333333333</v>
       </c>
       <c r="B70" t="n">
-        <v>1.6266</v>
+        <v>1.627</v>
       </c>
       <c r="C70" t="n">
         <v>69</v>
@@ -1551,7 +1551,7 @@
         <v>46112.53402777778</v>
       </c>
       <c r="B71" t="n">
-        <v>1.6264</v>
+        <v>1.6268</v>
       </c>
       <c r="C71" t="n">
         <v>70</v>
@@ -1567,7 +1567,7 @@
         <v>46112.53472222222</v>
       </c>
       <c r="B72" t="n">
-        <v>1.6265</v>
+        <v>1.6269</v>
       </c>
       <c r="C72" t="n">
         <v>71</v>
@@ -1583,7 +1583,7 @@
         <v>46112.53541666667</v>
       </c>
       <c r="B73" t="n">
-        <v>1.6266</v>
+        <v>1.627</v>
       </c>
       <c r="C73" t="n">
         <v>72</v>
@@ -1599,7 +1599,7 @@
         <v>46112.53611111111</v>
       </c>
       <c r="B74" t="n">
-        <v>1.6268</v>
+        <v>1.627</v>
       </c>
       <c r="C74" t="n">
         <v>73</v>
@@ -1615,7 +1615,7 @@
         <v>46112.53680555556</v>
       </c>
       <c r="B75" t="n">
-        <v>1.6269</v>
+        <v>1.627</v>
       </c>
       <c r="C75" t="n">
         <v>74</v>
@@ -1631,7 +1631,7 @@
         <v>46112.5375</v>
       </c>
       <c r="B76" t="n">
-        <v>1.6271</v>
+        <v>1.6272</v>
       </c>
       <c r="C76" t="n">
         <v>75</v>
@@ -1647,7 +1647,7 @@
         <v>46112.53819444445</v>
       </c>
       <c r="B77" t="n">
-        <v>1.6281</v>
+        <v>1.6275</v>
       </c>
       <c r="C77" t="n">
         <v>76</v>
@@ -1663,7 +1663,7 @@
         <v>46112.53888888889</v>
       </c>
       <c r="B78" t="n">
-        <v>1.6319</v>
+        <v>1.6317</v>
       </c>
       <c r="C78" t="n">
         <v>77</v>
@@ -1695,7 +1695,7 @@
         <v>46112.54027777778</v>
       </c>
       <c r="B80" t="n">
-        <v>1.6348</v>
+        <v>1.6349</v>
       </c>
       <c r="C80" t="n">
         <v>79</v>
@@ -1743,7 +1743,7 @@
         <v>46112.54236111111</v>
       </c>
       <c r="B83" t="n">
-        <v>1.6449</v>
+        <v>1.6455</v>
       </c>
       <c r="C83" t="n">
         <v>82</v>
@@ -1759,7 +1759,7 @@
         <v>46112.54305555556</v>
       </c>
       <c r="B84" t="n">
-        <v>1.6497</v>
+        <v>1.6494</v>
       </c>
       <c r="C84" t="n">
         <v>83</v>
@@ -1775,7 +1775,7 @@
         <v>46112.54375</v>
       </c>
       <c r="B85" t="n">
-        <v>1.6511</v>
+        <v>1.6512</v>
       </c>
       <c r="C85" t="n">
         <v>84</v>
@@ -1791,7 +1791,7 @@
         <v>46112.54444444444</v>
       </c>
       <c r="B86" t="n">
-        <v>1.6519</v>
+        <v>1.652</v>
       </c>
       <c r="C86" t="n">
         <v>85</v>
@@ -1807,7 +1807,7 @@
         <v>46112.54513888889</v>
       </c>
       <c r="B87" t="n">
-        <v>1.6514</v>
+        <v>1.6515</v>
       </c>
       <c r="C87" t="n">
         <v>86</v>
@@ -1823,7 +1823,7 @@
         <v>46112.54583333333</v>
       </c>
       <c r="B88" t="n">
-        <v>1.651</v>
+        <v>1.6511</v>
       </c>
       <c r="C88" t="n">
         <v>87</v>
@@ -1855,7 +1855,7 @@
         <v>46112.54722222222</v>
       </c>
       <c r="B90" t="n">
-        <v>1.6545</v>
+        <v>1.6539</v>
       </c>
       <c r="C90" t="n">
         <v>89</v>
@@ -1871,7 +1871,7 @@
         <v>46112.54791666667</v>
       </c>
       <c r="B91" t="n">
-        <v>1.657</v>
+        <v>1.6567</v>
       </c>
       <c r="C91" t="n">
         <v>90</v>
@@ -1887,7 +1887,7 @@
         <v>46112.54861111111</v>
       </c>
       <c r="B92" t="n">
-        <v>1.6577</v>
+        <v>1.6569</v>
       </c>
       <c r="C92" t="n">
         <v>91</v>
@@ -1903,7 +1903,7 @@
         <v>46112.54930555556</v>
       </c>
       <c r="B93" t="n">
-        <v>1.6622</v>
+        <v>1.6577</v>
       </c>
       <c r="C93" t="n">
         <v>92</v>
@@ -1919,7 +1919,7 @@
         <v>46112.55</v>
       </c>
       <c r="B94" t="n">
-        <v>1.6601</v>
+        <v>1.6606</v>
       </c>
       <c r="C94" t="n">
         <v>93</v>
@@ -1935,7 +1935,7 @@
         <v>46112.55069444444</v>
       </c>
       <c r="B95" t="n">
-        <v>1.6604</v>
+        <v>1.6599</v>
       </c>
       <c r="C95" t="n">
         <v>94</v>
@@ -1951,7 +1951,7 @@
         <v>46112.55138888889</v>
       </c>
       <c r="B96" t="n">
-        <v>1.6605</v>
+        <v>1.6609</v>
       </c>
       <c r="C96" t="n">
         <v>95</v>
@@ -2031,7 +2031,7 @@
         <v>46112.55486111111</v>
       </c>
       <c r="B101" t="n">
-        <v>1.6602</v>
+        <v>1.6603</v>
       </c>
       <c r="C101" t="n">
         <v>100</v>
@@ -2047,7 +2047,7 @@
         <v>46112.55555555555</v>
       </c>
       <c r="B102" t="n">
-        <v>1.6604</v>
+        <v>1.6605</v>
       </c>
       <c r="C102" t="n">
         <v>101</v>
@@ -2079,7 +2079,7 @@
         <v>46112.55694444444</v>
       </c>
       <c r="B104" t="n">
-        <v>1.6629</v>
+        <v>1.6626</v>
       </c>
       <c r="C104" t="n">
         <v>103</v>
@@ -2127,7 +2127,7 @@
         <v>46112.55902777778</v>
       </c>
       <c r="B107" t="n">
-        <v>1.6708</v>
+        <v>1.6707</v>
       </c>
       <c r="C107" t="n">
         <v>106</v>
@@ -2143,7 +2143,7 @@
         <v>46112.55972222222</v>
       </c>
       <c r="B108" t="n">
-        <v>1.6718</v>
+        <v>1.6717</v>
       </c>
       <c r="C108" t="n">
         <v>107</v>
@@ -2159,7 +2159,7 @@
         <v>46112.56041666667</v>
       </c>
       <c r="B109" t="n">
-        <v>1.6714</v>
+        <v>1.6711</v>
       </c>
       <c r="C109" t="n">
         <v>108</v>
@@ -2175,7 +2175,7 @@
         <v>46112.56111111111</v>
       </c>
       <c r="B110" t="n">
-        <v>1.6718</v>
+        <v>1.6712</v>
       </c>
       <c r="C110" t="n">
         <v>109</v>
@@ -2191,7 +2191,7 @@
         <v>46112.56180555555</v>
       </c>
       <c r="B111" t="n">
-        <v>1.6747</v>
+        <v>1.6748</v>
       </c>
       <c r="C111" t="n">
         <v>110</v>
@@ -2207,7 +2207,7 @@
         <v>46112.5625</v>
       </c>
       <c r="B112" t="n">
-        <v>1.6761</v>
+        <v>1.6757</v>
       </c>
       <c r="C112" t="n">
         <v>111</v>
@@ -2223,7 +2223,7 @@
         <v>46112.56319444445</v>
       </c>
       <c r="B113" t="n">
-        <v>1.6796</v>
+        <v>1.6791</v>
       </c>
       <c r="C113" t="n">
         <v>112</v>
@@ -2255,7 +2255,7 @@
         <v>46112.56458333333</v>
       </c>
       <c r="B115" t="n">
-        <v>1.6807</v>
+        <v>1.6808</v>
       </c>
       <c r="C115" t="n">
         <v>114</v>
@@ -2271,7 +2271,7 @@
         <v>46112.56527777778</v>
       </c>
       <c r="B116" t="n">
-        <v>1.6802</v>
+        <v>1.6801</v>
       </c>
       <c r="C116" t="n">
         <v>115</v>
@@ -2303,7 +2303,7 @@
         <v>46112.56666666667</v>
       </c>
       <c r="B118" t="n">
-        <v>1.6805</v>
+        <v>1.681</v>
       </c>
       <c r="C118" t="n">
         <v>117</v>
@@ -2319,7 +2319,7 @@
         <v>46112.56736111111</v>
       </c>
       <c r="B119" t="n">
-        <v>1.6803</v>
+        <v>1.6805</v>
       </c>
       <c r="C119" t="n">
         <v>118</v>
@@ -2367,7 +2367,7 @@
         <v>46112.56944444445</v>
       </c>
       <c r="B122" t="n">
-        <v>1.6802</v>
+        <v>1.6803</v>
       </c>
       <c r="C122" t="n">
         <v>121</v>
@@ -2383,7 +2383,7 @@
         <v>46112.57013888889</v>
       </c>
       <c r="B123" t="n">
-        <v>1.6804</v>
+        <v>1.6803</v>
       </c>
       <c r="C123" t="n">
         <v>122</v>
@@ -2399,7 +2399,7 @@
         <v>46112.57083333333</v>
       </c>
       <c r="B124" t="n">
-        <v>1.6807</v>
+        <v>1.681</v>
       </c>
       <c r="C124" t="n">
         <v>123</v>
@@ -2415,7 +2415,7 @@
         <v>46112.57152777778</v>
       </c>
       <c r="B125" t="n">
-        <v>1.6801</v>
+        <v>1.6809</v>
       </c>
       <c r="C125" t="n">
         <v>124</v>
@@ -2431,7 +2431,7 @@
         <v>46112.57222222222</v>
       </c>
       <c r="B126" t="n">
-        <v>1.6809</v>
+        <v>1.6811</v>
       </c>
       <c r="C126" t="n">
         <v>125</v>
@@ -2495,7 +2495,7 @@
         <v>46112.575</v>
       </c>
       <c r="B130" t="n">
-        <v>1.6735</v>
+        <v>1.6738</v>
       </c>
       <c r="C130" t="n">
         <v>129</v>
@@ -2511,7 +2511,7 @@
         <v>46112.57569444444</v>
       </c>
       <c r="B131" t="n">
-        <v>1.6718</v>
+        <v>1.6719</v>
       </c>
       <c r="C131" t="n">
         <v>130</v>
@@ -2527,7 +2527,7 @@
         <v>46112.57638888889</v>
       </c>
       <c r="B132" t="n">
-        <v>1.6683</v>
+        <v>1.6681</v>
       </c>
       <c r="C132" t="n">
         <v>131</v>
@@ -2543,7 +2543,7 @@
         <v>46112.57708333333</v>
       </c>
       <c r="B133" t="n">
-        <v>1.669</v>
+        <v>1.6692</v>
       </c>
       <c r="C133" t="n">
         <v>132</v>
@@ -2559,7 +2559,7 @@
         <v>46112.57777777778</v>
       </c>
       <c r="B134" t="n">
-        <v>1.664</v>
+        <v>1.6636</v>
       </c>
       <c r="C134" t="n">
         <v>133</v>
@@ -2575,7 +2575,7 @@
         <v>46112.57847222222</v>
       </c>
       <c r="B135" t="n">
-        <v>1.664</v>
+        <v>1.6642</v>
       </c>
       <c r="C135" t="n">
         <v>134</v>
@@ -2607,7 +2607,7 @@
         <v>46112.57986111111</v>
       </c>
       <c r="B137" t="n">
-        <v>1.6579</v>
+        <v>1.6578</v>
       </c>
       <c r="C137" t="n">
         <v>136</v>
@@ -2623,7 +2623,7 @@
         <v>46112.58055555556</v>
       </c>
       <c r="B138" t="n">
-        <v>1.6556</v>
+        <v>1.6576</v>
       </c>
       <c r="C138" t="n">
         <v>137</v>
@@ -2639,7 +2639,7 @@
         <v>46112.58125</v>
       </c>
       <c r="B139" t="n">
-        <v>1.6494</v>
+        <v>1.6552</v>
       </c>
       <c r="C139" t="n">
         <v>138</v>
@@ -2655,7 +2655,7 @@
         <v>46112.58194444444</v>
       </c>
       <c r="B140" t="n">
-        <v>1.6442</v>
+        <v>1.6496</v>
       </c>
       <c r="C140" t="n">
         <v>139</v>
@@ -2671,7 +2671,7 @@
         <v>46112.58263888889</v>
       </c>
       <c r="B141" t="n">
-        <v>1.6423</v>
+        <v>1.6446</v>
       </c>
       <c r="C141" t="n">
         <v>140</v>
@@ -2687,7 +2687,7 @@
         <v>46112.58333333334</v>
       </c>
       <c r="B142" t="n">
-        <v>1.638</v>
+        <v>1.6424</v>
       </c>
       <c r="C142" t="n">
         <v>141</v>
@@ -2703,7 +2703,7 @@
         <v>46112.58402777778</v>
       </c>
       <c r="B143" t="n">
-        <v>1.6374</v>
+        <v>1.6381</v>
       </c>
       <c r="C143" t="n">
         <v>142</v>
@@ -2719,7 +2719,7 @@
         <v>46112.58472222222</v>
       </c>
       <c r="B144" t="n">
-        <v>1.6331</v>
+        <v>1.6377</v>
       </c>
       <c r="C144" t="n">
         <v>143</v>
@@ -2735,7 +2735,7 @@
         <v>46112.58541666667</v>
       </c>
       <c r="B145" t="n">
-        <v>1.6367</v>
+        <v>1.6333</v>
       </c>
       <c r="C145" t="n">
         <v>144</v>
@@ -2751,7 +2751,7 @@
         <v>46112.58611111111</v>
       </c>
       <c r="B146" t="n">
-        <v>1.633</v>
+        <v>1.6369</v>
       </c>
       <c r="C146" t="n">
         <v>145</v>
@@ -2767,7 +2767,7 @@
         <v>46112.58680555555</v>
       </c>
       <c r="B147" t="n">
-        <v>1.6366</v>
+        <v>1.6342</v>
       </c>
       <c r="C147" t="n">
         <v>146</v>
@@ -2783,7 +2783,7 @@
         <v>46112.5875</v>
       </c>
       <c r="B148" t="n">
-        <v>1.6328</v>
+        <v>1.6366</v>
       </c>
       <c r="C148" t="n">
         <v>147</v>
@@ -2799,7 +2799,7 @@
         <v>46112.58819444444</v>
       </c>
       <c r="B149" t="n">
-        <v>1.6365</v>
+        <v>1.6324</v>
       </c>
       <c r="C149" t="n">
         <v>148</v>
@@ -2815,7 +2815,7 @@
         <v>46112.58888888889</v>
       </c>
       <c r="B150" t="n">
-        <v>1.6316</v>
+        <v>1.6294</v>
       </c>
       <c r="C150" t="n">
         <v>149</v>
@@ -2831,7 +2831,7 @@
         <v>46112.58958333333</v>
       </c>
       <c r="B151" t="n">
-        <v>1.6232</v>
+        <v>1.6241</v>
       </c>
       <c r="C151" t="n">
         <v>150</v>
@@ -2847,7 +2847,7 @@
         <v>46112.59027777778</v>
       </c>
       <c r="B152" t="n">
-        <v>1.6231</v>
+        <v>1.6215</v>
       </c>
       <c r="C152" t="n">
         <v>151</v>
@@ -2863,7 +2863,7 @@
         <v>46112.59097222222</v>
       </c>
       <c r="B153" t="n">
-        <v>1.6169</v>
+        <v>1.6199</v>
       </c>
       <c r="C153" t="n">
         <v>152</v>
@@ -2879,7 +2879,7 @@
         <v>46112.59166666667</v>
       </c>
       <c r="B154" t="n">
-        <v>1.62</v>
+        <v>1.6163</v>
       </c>
       <c r="C154" t="n">
         <v>153</v>
@@ -2895,7 +2895,7 @@
         <v>46112.59236111111</v>
       </c>
       <c r="B155" t="n">
-        <v>1.615</v>
+        <v>1.6199</v>
       </c>
       <c r="C155" t="n">
         <v>154</v>
@@ -2911,7 +2911,7 @@
         <v>46112.59305555555</v>
       </c>
       <c r="B156" t="n">
-        <v>1.6094</v>
+        <v>1.615</v>
       </c>
       <c r="C156" t="n">
         <v>155</v>
@@ -2927,7 +2927,7 @@
         <v>46112.59375</v>
       </c>
       <c r="B157" t="n">
-        <v>1.6089</v>
+        <v>1.6082</v>
       </c>
       <c r="C157" t="n">
         <v>156</v>
@@ -2943,7 +2943,7 @@
         <v>46112.59444444445</v>
       </c>
       <c r="B158" t="n">
-        <v>1.6067</v>
+        <v>1.609</v>
       </c>
       <c r="C158" t="n">
         <v>157</v>
@@ -2959,7 +2959,7 @@
         <v>46112.59513888889</v>
       </c>
       <c r="B159" t="n">
-        <v>1.6047</v>
+        <v>1.6076</v>
       </c>
       <c r="C159" t="n">
         <v>158</v>
@@ -2975,7 +2975,7 @@
         <v>46112.59583333333</v>
       </c>
       <c r="B160" t="n">
-        <v>1.6019</v>
+        <v>1.6084</v>
       </c>
       <c r="C160" t="n">
         <v>159</v>
@@ -2991,7 +2991,7 @@
         <v>46112.59652777778</v>
       </c>
       <c r="B161" t="n">
-        <v>1.5961</v>
+        <v>1.6054</v>
       </c>
       <c r="C161" t="n">
         <v>160</v>
@@ -3007,7 +3007,7 @@
         <v>46112.59722222222</v>
       </c>
       <c r="B162" t="n">
-        <v>1.5956</v>
+        <v>1.5994</v>
       </c>
       <c r="C162" t="n">
         <v>161</v>
@@ -3023,7 +3023,7 @@
         <v>46112.59791666667</v>
       </c>
       <c r="B163" t="n">
-        <v>1.5948</v>
+        <v>1.5957</v>
       </c>
       <c r="C163" t="n">
         <v>162</v>
@@ -3039,7 +3039,7 @@
         <v>46112.59861111111</v>
       </c>
       <c r="B164" t="n">
-        <v>1.5968</v>
+        <v>1.5958</v>
       </c>
       <c r="C164" t="n">
         <v>163</v>
@@ -3055,7 +3055,7 @@
         <v>46112.59930555556</v>
       </c>
       <c r="B165" t="n">
-        <v>1.5964</v>
+        <v>1.5975</v>
       </c>
       <c r="C165" t="n">
         <v>164</v>
@@ -3071,7 +3071,7 @@
         <v>46112.6</v>
       </c>
       <c r="B166" t="n">
-        <v>1.595</v>
+        <v>1.5958</v>
       </c>
       <c r="C166" t="n">
         <v>165</v>
@@ -3087,7 +3087,7 @@
         <v>46112.60069444445</v>
       </c>
       <c r="B167" t="n">
-        <v>1.5918</v>
+        <v>1.594</v>
       </c>
       <c r="C167" t="n">
         <v>166</v>
@@ -3103,7 +3103,7 @@
         <v>46112.60138888889</v>
       </c>
       <c r="B168" t="n">
-        <v>1.5826</v>
+        <v>1.5905</v>
       </c>
       <c r="C168" t="n">
         <v>167</v>
@@ -3119,7 +3119,7 @@
         <v>46112.60208333333</v>
       </c>
       <c r="B169" t="n">
-        <v>1.5855</v>
+        <v>1.5829</v>
       </c>
       <c r="C169" t="n">
         <v>168</v>
@@ -3135,7 +3135,7 @@
         <v>46112.60277777778</v>
       </c>
       <c r="B170" t="n">
-        <v>1.5822</v>
+        <v>1.5857</v>
       </c>
       <c r="C170" t="n">
         <v>169</v>
@@ -3151,7 +3151,7 @@
         <v>46112.60347222222</v>
       </c>
       <c r="B171" t="n">
-        <v>1.579</v>
+        <v>1.582</v>
       </c>
       <c r="C171" t="n">
         <v>170</v>
@@ -3167,7 +3167,7 @@
         <v>46112.60416666666</v>
       </c>
       <c r="B172" t="n">
-        <v>1.579</v>
+        <v>1.5792</v>
       </c>
       <c r="C172" t="n">
         <v>171</v>
@@ -3183,7 +3183,7 @@
         <v>46112.60486111111</v>
       </c>
       <c r="B173" t="n">
-        <v>1.5759</v>
+        <v>1.5789</v>
       </c>
       <c r="C173" t="n">
         <v>172</v>
@@ -3199,7 +3199,7 @@
         <v>46112.60555555556</v>
       </c>
       <c r="B174" t="n">
-        <v>1.5796</v>
+        <v>1.5736</v>
       </c>
       <c r="C174" t="n">
         <v>173</v>
@@ -3215,7 +3215,7 @@
         <v>46112.60625</v>
       </c>
       <c r="B175" t="n">
-        <v>1.5745</v>
+        <v>1.5759</v>
       </c>
       <c r="C175" t="n">
         <v>174</v>
@@ -3231,7 +3231,7 @@
         <v>46112.60694444444</v>
       </c>
       <c r="B176" t="n">
-        <v>1.576</v>
+        <v>1.5737</v>
       </c>
       <c r="C176" t="n">
         <v>175</v>
@@ -3247,7 +3247,7 @@
         <v>46112.60763888889</v>
       </c>
       <c r="B177" t="n">
-        <v>1.5736</v>
+        <v>1.5743</v>
       </c>
       <c r="C177" t="n">
         <v>176</v>
@@ -3263,7 +3263,7 @@
         <v>46112.60833333333</v>
       </c>
       <c r="B178" t="n">
-        <v>1.5729</v>
+        <v>1.5739</v>
       </c>
       <c r="C178" t="n">
         <v>177</v>
@@ -3279,7 +3279,7 @@
         <v>46112.60902777778</v>
       </c>
       <c r="B179" t="n">
-        <v>1.5733</v>
+        <v>1.5729</v>
       </c>
       <c r="C179" t="n">
         <v>178</v>
@@ -3295,7 +3295,7 @@
         <v>46112.60972222222</v>
       </c>
       <c r="B180" t="n">
-        <v>1.5746</v>
+        <v>1.5739</v>
       </c>
       <c r="C180" t="n">
         <v>179</v>
@@ -3311,7 +3311,7 @@
         <v>46112.61041666667</v>
       </c>
       <c r="B181" t="n">
-        <v>1.5761</v>
+        <v>1.5762</v>
       </c>
       <c r="C181" t="n">
         <v>180</v>

--- a/ML/DF6_futuro_3h.xlsx
+++ b/ML/DF6_futuro_3h.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,33 +435,33 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Previsto_Futuro</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Passo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46112.48611111111</v>
       </c>
       <c r="B2" t="n">
-        <v>1.5664</v>
+        <v>1.5631</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -459,11 +473,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46112.48680555556</v>
       </c>
       <c r="B3" t="n">
-        <v>1.5685</v>
+        <v>1.5674</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -475,11 +489,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46112.4875</v>
       </c>
       <c r="B4" t="n">
-        <v>1.5703</v>
+        <v>1.5685</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -491,7 +505,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46112.48819444444</v>
       </c>
       <c r="B5" t="n">
@@ -507,7 +521,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46112.48888888889</v>
       </c>
       <c r="B6" t="n">
@@ -523,11 +537,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46112.48958333334</v>
       </c>
       <c r="B7" t="n">
-        <v>1.57</v>
+        <v>1.5704</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -539,11 +553,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46112.49027777778</v>
       </c>
       <c r="B8" t="n">
-        <v>1.57</v>
+        <v>1.5703</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -555,11 +569,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46112.49097222222</v>
       </c>
       <c r="B9" t="n">
-        <v>1.5701</v>
+        <v>1.5708</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
@@ -571,7 +585,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46112.49166666667</v>
       </c>
       <c r="B10" t="n">
@@ -587,11 +601,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46112.49236111111</v>
       </c>
       <c r="B11" t="n">
-        <v>1.5766</v>
+        <v>1.5751</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
@@ -603,7 +617,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46112.49305555555</v>
       </c>
       <c r="B12" t="n">
@@ -619,7 +633,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46112.49375</v>
       </c>
       <c r="B13" t="n">
@@ -635,11 +649,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46112.49444444444</v>
       </c>
       <c r="B14" t="n">
-        <v>1.5801</v>
+        <v>1.58</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
@@ -651,11 +665,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46112.49513888889</v>
       </c>
       <c r="B15" t="n">
-        <v>1.58</v>
+        <v>1.5801</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
@@ -667,11 +681,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46112.49583333333</v>
       </c>
       <c r="B16" t="n">
-        <v>1.5869</v>
+        <v>1.5815</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
@@ -683,11 +697,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46112.49652777778</v>
       </c>
       <c r="B17" t="n">
-        <v>1.5895</v>
+        <v>1.5815</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
@@ -699,11 +713,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46112.49722222222</v>
       </c>
       <c r="B18" t="n">
-        <v>1.5906</v>
+        <v>1.582</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
@@ -715,11 +729,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46112.49791666667</v>
       </c>
       <c r="B19" t="n">
-        <v>1.5908</v>
+        <v>1.5823</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
@@ -731,11 +745,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46112.49861111111</v>
       </c>
       <c r="B20" t="n">
-        <v>1.5902</v>
+        <v>1.5845</v>
       </c>
       <c r="C20" t="n">
         <v>19</v>
@@ -747,11 +761,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46112.49930555555</v>
       </c>
       <c r="B21" t="n">
-        <v>1.5903</v>
+        <v>1.5882</v>
       </c>
       <c r="C21" t="n">
         <v>20</v>
@@ -763,11 +777,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46112.5</v>
       </c>
       <c r="B22" t="n">
-        <v>1.5903</v>
+        <v>1.59</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
@@ -779,11 +793,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46112.50069444445</v>
       </c>
       <c r="B23" t="n">
-        <v>1.5903</v>
+        <v>1.5902</v>
       </c>
       <c r="C23" t="n">
         <v>22</v>
@@ -795,11 +809,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46112.50138888889</v>
       </c>
       <c r="B24" t="n">
-        <v>1.5903</v>
+        <v>1.592</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
@@ -811,11 +825,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46112.50208333333</v>
       </c>
       <c r="B25" t="n">
-        <v>1.5934</v>
+        <v>1.5922</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -827,11 +841,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46112.50277777778</v>
       </c>
       <c r="B26" t="n">
-        <v>1.5989</v>
+        <v>1.5922</v>
       </c>
       <c r="C26" t="n">
         <v>25</v>
@@ -843,11 +857,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46112.50347222222</v>
       </c>
       <c r="B27" t="n">
-        <v>1.6</v>
+        <v>1.5922</v>
       </c>
       <c r="C27" t="n">
         <v>26</v>
@@ -859,11 +873,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46112.50416666667</v>
       </c>
       <c r="B28" t="n">
-        <v>1.6</v>
+        <v>1.5922</v>
       </c>
       <c r="C28" t="n">
         <v>27</v>
@@ -875,11 +889,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46112.50486111111</v>
       </c>
       <c r="B29" t="n">
-        <v>1.6</v>
+        <v>1.5922</v>
       </c>
       <c r="C29" t="n">
         <v>28</v>
@@ -891,11 +905,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46112.50555555556</v>
       </c>
       <c r="B30" t="n">
-        <v>1.6</v>
+        <v>1.5928</v>
       </c>
       <c r="C30" t="n">
         <v>29</v>
@@ -907,11 +921,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46112.50625</v>
       </c>
       <c r="B31" t="n">
-        <v>1.6</v>
+        <v>1.5992</v>
       </c>
       <c r="C31" t="n">
         <v>30</v>
@@ -923,7 +937,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46112.50694444445</v>
       </c>
       <c r="B32" t="n">
@@ -939,11 +953,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46112.50763888889</v>
       </c>
       <c r="B33" t="n">
-        <v>1.6001</v>
+        <v>1.6</v>
       </c>
       <c r="C33" t="n">
         <v>32</v>
@@ -955,11 +969,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46112.50833333333</v>
       </c>
       <c r="B34" t="n">
-        <v>1.6028</v>
+        <v>1.6</v>
       </c>
       <c r="C34" t="n">
         <v>33</v>
@@ -971,11 +985,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46112.50902777778</v>
       </c>
       <c r="B35" t="n">
-        <v>1.6069</v>
+        <v>1.6</v>
       </c>
       <c r="C35" t="n">
         <v>34</v>
@@ -987,11 +1001,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46112.50972222222</v>
       </c>
       <c r="B36" t="n">
-        <v>1.6069</v>
+        <v>1.6</v>
       </c>
       <c r="C36" t="n">
         <v>35</v>
@@ -1003,11 +1017,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46112.51041666666</v>
       </c>
       <c r="B37" t="n">
-        <v>1.6068</v>
+        <v>1.6014</v>
       </c>
       <c r="C37" t="n">
         <v>36</v>
@@ -1019,11 +1033,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46112.51111111111</v>
       </c>
       <c r="B38" t="n">
-        <v>1.6069</v>
+        <v>1.6004</v>
       </c>
       <c r="C38" t="n">
         <v>37</v>
@@ -1035,11 +1049,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46112.51180555556</v>
       </c>
       <c r="B39" t="n">
-        <v>1.6072</v>
+        <v>1.6014</v>
       </c>
       <c r="C39" t="n">
         <v>38</v>
@@ -1051,11 +1065,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46112.5125</v>
       </c>
       <c r="B40" t="n">
-        <v>1.6074</v>
+        <v>1.6036</v>
       </c>
       <c r="C40" t="n">
         <v>39</v>
@@ -1067,11 +1081,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46112.51319444444</v>
       </c>
       <c r="B41" t="n">
-        <v>1.6082</v>
+        <v>1.6085</v>
       </c>
       <c r="C41" t="n">
         <v>40</v>
@@ -1083,11 +1097,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46112.51388888889</v>
       </c>
       <c r="B42" t="n">
-        <v>1.611</v>
+        <v>1.6103</v>
       </c>
       <c r="C42" t="n">
         <v>41</v>
@@ -1099,11 +1113,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46112.51458333333</v>
       </c>
       <c r="B43" t="n">
-        <v>1.61</v>
+        <v>1.6104</v>
       </c>
       <c r="C43" t="n">
         <v>42</v>
@@ -1115,11 +1129,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46112.51527777778</v>
       </c>
       <c r="B44" t="n">
-        <v>1.61</v>
+        <v>1.6107</v>
       </c>
       <c r="C44" t="n">
         <v>43</v>
@@ -1131,11 +1145,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46112.51597222222</v>
       </c>
       <c r="B45" t="n">
-        <v>1.6104</v>
+        <v>1.6109</v>
       </c>
       <c r="C45" t="n">
         <v>44</v>
@@ -1147,11 +1161,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46112.51666666667</v>
       </c>
       <c r="B46" t="n">
-        <v>1.6106</v>
+        <v>1.6121</v>
       </c>
       <c r="C46" t="n">
         <v>45</v>
@@ -1163,11 +1177,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46112.51736111111</v>
       </c>
       <c r="B47" t="n">
-        <v>1.6103</v>
+        <v>1.6162</v>
       </c>
       <c r="C47" t="n">
         <v>46</v>
@@ -1179,11 +1193,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46112.51805555556</v>
       </c>
       <c r="B48" t="n">
-        <v>1.6103</v>
+        <v>1.6206</v>
       </c>
       <c r="C48" t="n">
         <v>47</v>
@@ -1195,11 +1209,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46112.51875</v>
       </c>
       <c r="B49" t="n">
-        <v>1.6119</v>
+        <v>1.6207</v>
       </c>
       <c r="C49" t="n">
         <v>48</v>
@@ -1211,11 +1225,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46112.51944444444</v>
       </c>
       <c r="B50" t="n">
-        <v>1.6148</v>
+        <v>1.621</v>
       </c>
       <c r="C50" t="n">
         <v>49</v>
@@ -1227,11 +1241,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46112.52013888889</v>
       </c>
       <c r="B51" t="n">
-        <v>1.6111</v>
+        <v>1.6213</v>
       </c>
       <c r="C51" t="n">
         <v>50</v>
@@ -1243,11 +1257,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46112.52083333334</v>
       </c>
       <c r="B52" t="n">
-        <v>1.6156</v>
+        <v>1.6232</v>
       </c>
       <c r="C52" t="n">
         <v>51</v>
@@ -1259,11 +1273,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46112.52152777778</v>
       </c>
       <c r="B53" t="n">
-        <v>1.6237</v>
+        <v>1.6265</v>
       </c>
       <c r="C53" t="n">
         <v>52</v>
@@ -1275,11 +1289,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46112.52222222222</v>
       </c>
       <c r="B54" t="n">
-        <v>1.6231</v>
+        <v>1.6268</v>
       </c>
       <c r="C54" t="n">
         <v>53</v>
@@ -1291,11 +1305,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46112.52291666667</v>
       </c>
       <c r="B55" t="n">
-        <v>1.6241</v>
+        <v>1.6274</v>
       </c>
       <c r="C55" t="n">
         <v>54</v>
@@ -1307,11 +1321,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46112.52361111111</v>
       </c>
       <c r="B56" t="n">
-        <v>1.6237</v>
+        <v>1.627</v>
       </c>
       <c r="C56" t="n">
         <v>55</v>
@@ -1323,11 +1337,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46112.52430555555</v>
       </c>
       <c r="B57" t="n">
-        <v>1.6234</v>
+        <v>1.6267</v>
       </c>
       <c r="C57" t="n">
         <v>56</v>
@@ -1339,11 +1353,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46112.525</v>
       </c>
       <c r="B58" t="n">
-        <v>1.6238</v>
+        <v>1.6266</v>
       </c>
       <c r="C58" t="n">
         <v>57</v>
@@ -1355,11 +1369,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46112.52569444444</v>
       </c>
       <c r="B59" t="n">
-        <v>1.6261</v>
+        <v>1.6272</v>
       </c>
       <c r="C59" t="n">
         <v>58</v>
@@ -1371,11 +1385,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46112.52638888889</v>
       </c>
       <c r="B60" t="n">
-        <v>1.6264</v>
+        <v>1.6274</v>
       </c>
       <c r="C60" t="n">
         <v>59</v>
@@ -1387,11 +1401,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46112.52708333333</v>
       </c>
       <c r="B61" t="n">
-        <v>1.6261</v>
+        <v>1.6271</v>
       </c>
       <c r="C61" t="n">
         <v>60</v>
@@ -1403,11 +1417,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46112.52777777778</v>
       </c>
       <c r="B62" t="n">
-        <v>1.6257</v>
+        <v>1.6269</v>
       </c>
       <c r="C62" t="n">
         <v>61</v>
@@ -1419,11 +1433,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46112.52847222222</v>
       </c>
       <c r="B63" t="n">
-        <v>1.6267</v>
+        <v>1.6274</v>
       </c>
       <c r="C63" t="n">
         <v>62</v>
@@ -1435,11 +1449,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46112.52916666667</v>
       </c>
       <c r="B64" t="n">
-        <v>1.6271</v>
+        <v>1.6269</v>
       </c>
       <c r="C64" t="n">
         <v>63</v>
@@ -1451,11 +1465,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46112.52986111111</v>
       </c>
       <c r="B65" t="n">
-        <v>1.627</v>
+        <v>1.6274</v>
       </c>
       <c r="C65" t="n">
         <v>64</v>
@@ -1467,11 +1481,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46112.53055555555</v>
       </c>
       <c r="B66" t="n">
-        <v>1.6263</v>
+        <v>1.6265</v>
       </c>
       <c r="C66" t="n">
         <v>65</v>
@@ -1483,11 +1497,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46112.53125</v>
       </c>
       <c r="B67" t="n">
-        <v>1.6269</v>
+        <v>1.6266</v>
       </c>
       <c r="C67" t="n">
         <v>66</v>
@@ -1499,11 +1513,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112.53194444445</v>
       </c>
       <c r="B68" t="n">
-        <v>1.627</v>
+        <v>1.6272</v>
       </c>
       <c r="C68" t="n">
         <v>67</v>
@@ -1515,11 +1529,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112.53263888889</v>
       </c>
       <c r="B69" t="n">
-        <v>1.627</v>
+        <v>1.6268</v>
       </c>
       <c r="C69" t="n">
         <v>68</v>
@@ -1531,11 +1545,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46112.53333333333</v>
       </c>
       <c r="B70" t="n">
-        <v>1.627</v>
+        <v>1.6271</v>
       </c>
       <c r="C70" t="n">
         <v>69</v>
@@ -1547,11 +1561,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46112.53402777778</v>
       </c>
       <c r="B71" t="n">
-        <v>1.6268</v>
+        <v>1.6273</v>
       </c>
       <c r="C71" t="n">
         <v>70</v>
@@ -1563,11 +1577,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46112.53472222222</v>
       </c>
       <c r="B72" t="n">
-        <v>1.6269</v>
+        <v>1.6275</v>
       </c>
       <c r="C72" t="n">
         <v>71</v>
@@ -1579,11 +1593,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46112.53541666667</v>
       </c>
       <c r="B73" t="n">
-        <v>1.627</v>
+        <v>1.6353</v>
       </c>
       <c r="C73" t="n">
         <v>72</v>
@@ -1595,11 +1609,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46112.53611111111</v>
       </c>
       <c r="B74" t="n">
-        <v>1.627</v>
+        <v>1.64</v>
       </c>
       <c r="C74" t="n">
         <v>73</v>
@@ -1611,11 +1625,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46112.53680555556</v>
       </c>
       <c r="B75" t="n">
-        <v>1.627</v>
+        <v>1.6401</v>
       </c>
       <c r="C75" t="n">
         <v>74</v>
@@ -1627,11 +1641,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46112.5375</v>
       </c>
       <c r="B76" t="n">
-        <v>1.6272</v>
+        <v>1.6421</v>
       </c>
       <c r="C76" t="n">
         <v>75</v>
@@ -1643,11 +1657,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46112.53819444445</v>
       </c>
       <c r="B77" t="n">
-        <v>1.6275</v>
+        <v>1.6419</v>
       </c>
       <c r="C77" t="n">
         <v>76</v>
@@ -1659,11 +1673,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46112.53888888889</v>
       </c>
       <c r="B78" t="n">
-        <v>1.6317</v>
+        <v>1.6429</v>
       </c>
       <c r="C78" t="n">
         <v>77</v>
@@ -1675,11 +1689,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46112.53958333333</v>
       </c>
       <c r="B79" t="n">
-        <v>1.6307</v>
+        <v>1.6491</v>
       </c>
       <c r="C79" t="n">
         <v>78</v>
@@ -1691,11 +1705,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46112.54027777778</v>
       </c>
       <c r="B80" t="n">
-        <v>1.6349</v>
+        <v>1.6506</v>
       </c>
       <c r="C80" t="n">
         <v>79</v>
@@ -1707,11 +1721,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46112.54097222222</v>
       </c>
       <c r="B81" t="n">
-        <v>1.6392</v>
+        <v>1.6521</v>
       </c>
       <c r="C81" t="n">
         <v>80</v>
@@ -1723,11 +1737,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46112.54166666666</v>
       </c>
       <c r="B82" t="n">
-        <v>1.6401</v>
+        <v>1.6529</v>
       </c>
       <c r="C82" t="n">
         <v>81</v>
@@ -1739,11 +1753,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46112.54236111111</v>
       </c>
       <c r="B83" t="n">
-        <v>1.6455</v>
+        <v>1.6576</v>
       </c>
       <c r="C83" t="n">
         <v>82</v>
@@ -1755,11 +1769,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46112.54305555556</v>
       </c>
       <c r="B84" t="n">
-        <v>1.6494</v>
+        <v>1.6601</v>
       </c>
       <c r="C84" t="n">
         <v>83</v>
@@ -1771,11 +1785,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46112.54375</v>
       </c>
       <c r="B85" t="n">
-        <v>1.6512</v>
+        <v>1.661</v>
       </c>
       <c r="C85" t="n">
         <v>84</v>
@@ -1787,11 +1801,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46112.54444444444</v>
       </c>
       <c r="B86" t="n">
-        <v>1.652</v>
+        <v>1.661</v>
       </c>
       <c r="C86" t="n">
         <v>85</v>
@@ -1803,11 +1817,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46112.54513888889</v>
       </c>
       <c r="B87" t="n">
-        <v>1.6515</v>
+        <v>1.6604</v>
       </c>
       <c r="C87" t="n">
         <v>86</v>
@@ -1819,11 +1833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46112.54583333333</v>
       </c>
       <c r="B88" t="n">
-        <v>1.6511</v>
+        <v>1.6602</v>
       </c>
       <c r="C88" t="n">
         <v>87</v>
@@ -1835,11 +1849,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46112.54652777778</v>
       </c>
       <c r="B89" t="n">
-        <v>1.6512</v>
+        <v>1.6606</v>
       </c>
       <c r="C89" t="n">
         <v>88</v>
@@ -1851,11 +1865,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46112.54722222222</v>
       </c>
       <c r="B90" t="n">
-        <v>1.6539</v>
+        <v>1.6613</v>
       </c>
       <c r="C90" t="n">
         <v>89</v>
@@ -1867,11 +1881,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46112.54791666667</v>
       </c>
       <c r="B91" t="n">
-        <v>1.6567</v>
+        <v>1.6614</v>
       </c>
       <c r="C91" t="n">
         <v>90</v>
@@ -1883,11 +1897,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46112.54861111111</v>
       </c>
       <c r="B92" t="n">
-        <v>1.6569</v>
+        <v>1.6625</v>
       </c>
       <c r="C92" t="n">
         <v>91</v>
@@ -1899,11 +1913,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46112.54930555556</v>
       </c>
       <c r="B93" t="n">
-        <v>1.6577</v>
+        <v>1.6681</v>
       </c>
       <c r="C93" t="n">
         <v>92</v>
@@ -1915,11 +1929,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46112.55</v>
       </c>
       <c r="B94" t="n">
-        <v>1.6606</v>
+        <v>1.67</v>
       </c>
       <c r="C94" t="n">
         <v>93</v>
@@ -1931,11 +1945,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46112.55069444444</v>
       </c>
       <c r="B95" t="n">
-        <v>1.6599</v>
+        <v>1.6704</v>
       </c>
       <c r="C95" t="n">
         <v>94</v>
@@ -1947,11 +1961,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46112.55138888889</v>
       </c>
       <c r="B96" t="n">
-        <v>1.6609</v>
+        <v>1.6703</v>
       </c>
       <c r="C96" t="n">
         <v>95</v>
@@ -1963,11 +1977,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46112.55208333334</v>
       </c>
       <c r="B97" t="n">
-        <v>1.66</v>
+        <v>1.6706</v>
       </c>
       <c r="C97" t="n">
         <v>96</v>
@@ -1979,11 +1993,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>46112.55277777778</v>
       </c>
       <c r="B98" t="n">
-        <v>1.6602</v>
+        <v>1.6704</v>
       </c>
       <c r="C98" t="n">
         <v>97</v>
@@ -1995,11 +2009,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>46112.55347222222</v>
       </c>
       <c r="B99" t="n">
-        <v>1.66</v>
+        <v>1.6704</v>
       </c>
       <c r="C99" t="n">
         <v>98</v>
@@ -2011,11 +2025,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>46112.55416666667</v>
       </c>
       <c r="B100" t="n">
-        <v>1.66</v>
+        <v>1.6711</v>
       </c>
       <c r="C100" t="n">
         <v>99</v>
@@ -2027,11 +2041,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>46112.55486111111</v>
       </c>
       <c r="B101" t="n">
-        <v>1.6603</v>
+        <v>1.6706</v>
       </c>
       <c r="C101" t="n">
         <v>100</v>
@@ -2043,11 +2057,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>46112.55555555555</v>
       </c>
       <c r="B102" t="n">
-        <v>1.6605</v>
+        <v>1.6719</v>
       </c>
       <c r="C102" t="n">
         <v>101</v>
@@ -2059,11 +2073,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>46112.55625</v>
       </c>
       <c r="B103" t="n">
-        <v>1.6604</v>
+        <v>1.6726</v>
       </c>
       <c r="C103" t="n">
         <v>102</v>
@@ -2075,11 +2089,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>46112.55694444444</v>
       </c>
       <c r="B104" t="n">
-        <v>1.6626</v>
+        <v>1.6773</v>
       </c>
       <c r="C104" t="n">
         <v>103</v>
@@ -2091,11 +2105,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>46112.55763888889</v>
       </c>
       <c r="B105" t="n">
-        <v>1.6681</v>
+        <v>1.68</v>
       </c>
       <c r="C105" t="n">
         <v>104</v>
@@ -2107,11 +2121,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>46112.55833333333</v>
       </c>
       <c r="B106" t="n">
-        <v>1.67</v>
+        <v>1.6801</v>
       </c>
       <c r="C106" t="n">
         <v>105</v>
@@ -2123,11 +2137,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>46112.55902777778</v>
       </c>
       <c r="B107" t="n">
-        <v>1.6707</v>
+        <v>1.6802</v>
       </c>
       <c r="C107" t="n">
         <v>106</v>
@@ -2139,11 +2153,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>46112.55972222222</v>
       </c>
       <c r="B108" t="n">
-        <v>1.6717</v>
+        <v>1.6803</v>
       </c>
       <c r="C108" t="n">
         <v>107</v>
@@ -2155,11 +2169,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>46112.56041666667</v>
       </c>
       <c r="B109" t="n">
-        <v>1.6711</v>
+        <v>1.6802</v>
       </c>
       <c r="C109" t="n">
         <v>108</v>
@@ -2171,11 +2185,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>46112.56111111111</v>
       </c>
       <c r="B110" t="n">
-        <v>1.6712</v>
+        <v>1.6802</v>
       </c>
       <c r="C110" t="n">
         <v>109</v>
@@ -2187,11 +2201,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>46112.56180555555</v>
       </c>
       <c r="B111" t="n">
-        <v>1.6748</v>
+        <v>1.6801</v>
       </c>
       <c r="C111" t="n">
         <v>110</v>
@@ -2203,11 +2217,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>46112.5625</v>
       </c>
       <c r="B112" t="n">
-        <v>1.6757</v>
+        <v>1.68</v>
       </c>
       <c r="C112" t="n">
         <v>111</v>
@@ -2219,11 +2233,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>46112.56319444445</v>
       </c>
       <c r="B113" t="n">
-        <v>1.6791</v>
+        <v>1.68</v>
       </c>
       <c r="C113" t="n">
         <v>112</v>
@@ -2235,7 +2249,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46112.56388888889</v>
       </c>
       <c r="B114" t="n">
@@ -2251,11 +2265,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46112.56458333333</v>
       </c>
       <c r="B115" t="n">
-        <v>1.6808</v>
+        <v>1.68</v>
       </c>
       <c r="C115" t="n">
         <v>114</v>
@@ -2267,11 +2281,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46112.56527777778</v>
       </c>
       <c r="B116" t="n">
-        <v>1.6801</v>
+        <v>1.68</v>
       </c>
       <c r="C116" t="n">
         <v>115</v>
@@ -2283,11 +2297,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46112.56597222222</v>
       </c>
       <c r="B117" t="n">
-        <v>1.6803</v>
+        <v>1.6802</v>
       </c>
       <c r="C117" t="n">
         <v>116</v>
@@ -2299,11 +2313,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46112.56666666667</v>
       </c>
       <c r="B118" t="n">
-        <v>1.681</v>
+        <v>1.6802</v>
       </c>
       <c r="C118" t="n">
         <v>117</v>
@@ -2315,11 +2329,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46112.56736111111</v>
       </c>
       <c r="B119" t="n">
-        <v>1.6805</v>
+        <v>1.68</v>
       </c>
       <c r="C119" t="n">
         <v>118</v>
@@ -2331,11 +2345,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46112.56805555556</v>
       </c>
       <c r="B120" t="n">
-        <v>1.6802</v>
+        <v>1.68</v>
       </c>
       <c r="C120" t="n">
         <v>119</v>
@@ -2347,11 +2361,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46112.56875</v>
       </c>
       <c r="B121" t="n">
-        <v>1.6802</v>
+        <v>1.68</v>
       </c>
       <c r="C121" t="n">
         <v>120</v>
@@ -2363,11 +2377,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46112.56944444445</v>
       </c>
       <c r="B122" t="n">
-        <v>1.6803</v>
+        <v>1.68</v>
       </c>
       <c r="C122" t="n">
         <v>121</v>
@@ -2379,11 +2393,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46112.57013888889</v>
       </c>
       <c r="B123" t="n">
-        <v>1.6803</v>
+        <v>1.6805</v>
       </c>
       <c r="C123" t="n">
         <v>122</v>
@@ -2395,11 +2409,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46112.57083333333</v>
       </c>
       <c r="B124" t="n">
-        <v>1.681</v>
+        <v>1.6802</v>
       </c>
       <c r="C124" t="n">
         <v>123</v>
@@ -2411,11 +2425,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46112.57152777778</v>
       </c>
       <c r="B125" t="n">
-        <v>1.6809</v>
+        <v>1.6802</v>
       </c>
       <c r="C125" t="n">
         <v>124</v>
@@ -2427,11 +2441,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46112.57222222222</v>
       </c>
       <c r="B126" t="n">
-        <v>1.6811</v>
+        <v>1.6802</v>
       </c>
       <c r="C126" t="n">
         <v>125</v>
@@ -2443,11 +2457,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46112.57291666666</v>
       </c>
       <c r="B127" t="n">
-        <v>1.68</v>
+        <v>1.6802</v>
       </c>
       <c r="C127" t="n">
         <v>126</v>
@@ -2459,11 +2473,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46112.57361111111</v>
       </c>
       <c r="B128" t="n">
-        <v>1.6791</v>
+        <v>1.6802</v>
       </c>
       <c r="C128" t="n">
         <v>127</v>
@@ -2475,11 +2489,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46112.57430555556</v>
       </c>
       <c r="B129" t="n">
-        <v>1.676</v>
+        <v>1.6802</v>
       </c>
       <c r="C129" t="n">
         <v>128</v>
@@ -2491,11 +2505,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46112.575</v>
       </c>
       <c r="B130" t="n">
-        <v>1.6738</v>
+        <v>1.6802</v>
       </c>
       <c r="C130" t="n">
         <v>129</v>
@@ -2507,11 +2521,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46112.57569444444</v>
       </c>
       <c r="B131" t="n">
-        <v>1.6719</v>
+        <v>1.6802</v>
       </c>
       <c r="C131" t="n">
         <v>130</v>
@@ -2523,11 +2537,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46112.57638888889</v>
       </c>
       <c r="B132" t="n">
-        <v>1.6681</v>
+        <v>1.6802</v>
       </c>
       <c r="C132" t="n">
         <v>131</v>
@@ -2539,11 +2553,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46112.57708333333</v>
       </c>
       <c r="B133" t="n">
-        <v>1.6692</v>
+        <v>1.6802</v>
       </c>
       <c r="C133" t="n">
         <v>132</v>
@@ -2555,11 +2569,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46112.57777777778</v>
       </c>
       <c r="B134" t="n">
-        <v>1.6636</v>
+        <v>1.6802</v>
       </c>
       <c r="C134" t="n">
         <v>133</v>
@@ -2571,11 +2585,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46112.57847222222</v>
       </c>
       <c r="B135" t="n">
-        <v>1.6642</v>
+        <v>1.6802</v>
       </c>
       <c r="C135" t="n">
         <v>134</v>
@@ -2587,11 +2601,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46112.57916666667</v>
       </c>
       <c r="B136" t="n">
-        <v>1.6603</v>
+        <v>1.6802</v>
       </c>
       <c r="C136" t="n">
         <v>135</v>
@@ -2603,11 +2617,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>46112.57986111111</v>
       </c>
       <c r="B137" t="n">
-        <v>1.6578</v>
+        <v>1.6802</v>
       </c>
       <c r="C137" t="n">
         <v>136</v>
@@ -2619,11 +2633,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>46112.58055555556</v>
       </c>
       <c r="B138" t="n">
-        <v>1.6576</v>
+        <v>1.6802</v>
       </c>
       <c r="C138" t="n">
         <v>137</v>
@@ -2635,11 +2649,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>46112.58125</v>
       </c>
       <c r="B139" t="n">
-        <v>1.6552</v>
+        <v>1.6802</v>
       </c>
       <c r="C139" t="n">
         <v>138</v>
@@ -2651,11 +2665,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46112.58194444444</v>
       </c>
       <c r="B140" t="n">
-        <v>1.6496</v>
+        <v>1.6802</v>
       </c>
       <c r="C140" t="n">
         <v>139</v>
@@ -2667,11 +2681,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46112.58263888889</v>
       </c>
       <c r="B141" t="n">
-        <v>1.6446</v>
+        <v>1.6802</v>
       </c>
       <c r="C141" t="n">
         <v>140</v>
@@ -2683,11 +2697,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46112.58333333334</v>
       </c>
       <c r="B142" t="n">
-        <v>1.6424</v>
+        <v>1.6801</v>
       </c>
       <c r="C142" t="n">
         <v>141</v>
@@ -2699,11 +2713,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46112.58402777778</v>
       </c>
       <c r="B143" t="n">
-        <v>1.6381</v>
+        <v>1.6801</v>
       </c>
       <c r="C143" t="n">
         <v>142</v>
@@ -2715,11 +2729,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46112.58472222222</v>
       </c>
       <c r="B144" t="n">
-        <v>1.6377</v>
+        <v>1.6801</v>
       </c>
       <c r="C144" t="n">
         <v>143</v>
@@ -2731,11 +2745,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46112.58541666667</v>
       </c>
       <c r="B145" t="n">
-        <v>1.6333</v>
+        <v>1.6801</v>
       </c>
       <c r="C145" t="n">
         <v>144</v>
@@ -2747,11 +2761,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>46112.58611111111</v>
       </c>
       <c r="B146" t="n">
-        <v>1.6369</v>
+        <v>1.6801</v>
       </c>
       <c r="C146" t="n">
         <v>145</v>
@@ -2763,11 +2777,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>46112.58680555555</v>
       </c>
       <c r="B147" t="n">
-        <v>1.6342</v>
+        <v>1.6801</v>
       </c>
       <c r="C147" t="n">
         <v>146</v>
@@ -2779,11 +2793,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>46112.5875</v>
       </c>
       <c r="B148" t="n">
-        <v>1.6366</v>
+        <v>1.6801</v>
       </c>
       <c r="C148" t="n">
         <v>147</v>
@@ -2795,11 +2809,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>46112.58819444444</v>
       </c>
       <c r="B149" t="n">
-        <v>1.6324</v>
+        <v>1.6801</v>
       </c>
       <c r="C149" t="n">
         <v>148</v>
@@ -2811,11 +2825,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>46112.58888888889</v>
       </c>
       <c r="B150" t="n">
-        <v>1.6294</v>
+        <v>1.6801</v>
       </c>
       <c r="C150" t="n">
         <v>149</v>
@@ -2827,11 +2841,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>46112.58958333333</v>
       </c>
       <c r="B151" t="n">
-        <v>1.6241</v>
+        <v>1.6801</v>
       </c>
       <c r="C151" t="n">
         <v>150</v>
@@ -2843,11 +2857,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>46112.59027777778</v>
       </c>
       <c r="B152" t="n">
-        <v>1.6215</v>
+        <v>1.6801</v>
       </c>
       <c r="C152" t="n">
         <v>151</v>
@@ -2859,11 +2873,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>46112.59097222222</v>
       </c>
       <c r="B153" t="n">
-        <v>1.6199</v>
+        <v>1.6801</v>
       </c>
       <c r="C153" t="n">
         <v>152</v>
@@ -2875,11 +2889,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>46112.59166666667</v>
       </c>
       <c r="B154" t="n">
-        <v>1.6163</v>
+        <v>1.6801</v>
       </c>
       <c r="C154" t="n">
         <v>153</v>
@@ -2891,11 +2905,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>46112.59236111111</v>
       </c>
       <c r="B155" t="n">
-        <v>1.6199</v>
+        <v>1.6801</v>
       </c>
       <c r="C155" t="n">
         <v>154</v>
@@ -2907,11 +2921,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46112.59305555555</v>
       </c>
       <c r="B156" t="n">
-        <v>1.615</v>
+        <v>1.6801</v>
       </c>
       <c r="C156" t="n">
         <v>155</v>
@@ -2923,11 +2937,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46112.59375</v>
       </c>
       <c r="B157" t="n">
-        <v>1.6082</v>
+        <v>1.6801</v>
       </c>
       <c r="C157" t="n">
         <v>156</v>
@@ -2939,11 +2953,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46112.59444444445</v>
       </c>
       <c r="B158" t="n">
-        <v>1.609</v>
+        <v>1.6801</v>
       </c>
       <c r="C158" t="n">
         <v>157</v>
@@ -2955,11 +2969,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46112.59513888889</v>
       </c>
       <c r="B159" t="n">
-        <v>1.6076</v>
+        <v>1.6801</v>
       </c>
       <c r="C159" t="n">
         <v>158</v>
@@ -2971,11 +2985,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46112.59583333333</v>
       </c>
       <c r="B160" t="n">
-        <v>1.6084</v>
+        <v>1.6801</v>
       </c>
       <c r="C160" t="n">
         <v>159</v>
@@ -2987,11 +3001,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46112.59652777778</v>
       </c>
       <c r="B161" t="n">
-        <v>1.6054</v>
+        <v>1.6801</v>
       </c>
       <c r="C161" t="n">
         <v>160</v>
@@ -3003,11 +3017,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46112.59722222222</v>
       </c>
       <c r="B162" t="n">
-        <v>1.5994</v>
+        <v>1.6801</v>
       </c>
       <c r="C162" t="n">
         <v>161</v>
@@ -3019,11 +3033,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46112.59791666667</v>
       </c>
       <c r="B163" t="n">
-        <v>1.5957</v>
+        <v>1.6801</v>
       </c>
       <c r="C163" t="n">
         <v>162</v>
@@ -3035,11 +3049,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46112.59861111111</v>
       </c>
       <c r="B164" t="n">
-        <v>1.5958</v>
+        <v>1.6801</v>
       </c>
       <c r="C164" t="n">
         <v>163</v>
@@ -3051,11 +3065,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46112.59930555556</v>
       </c>
       <c r="B165" t="n">
-        <v>1.5975</v>
+        <v>1.6801</v>
       </c>
       <c r="C165" t="n">
         <v>164</v>
@@ -3067,11 +3081,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46112.6</v>
       </c>
       <c r="B166" t="n">
-        <v>1.5958</v>
+        <v>1.6801</v>
       </c>
       <c r="C166" t="n">
         <v>165</v>
@@ -3083,11 +3097,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46112.60069444445</v>
       </c>
       <c r="B167" t="n">
-        <v>1.594</v>
+        <v>1.6801</v>
       </c>
       <c r="C167" t="n">
         <v>166</v>
@@ -3099,11 +3113,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46112.60138888889</v>
       </c>
       <c r="B168" t="n">
-        <v>1.5905</v>
+        <v>1.6801</v>
       </c>
       <c r="C168" t="n">
         <v>167</v>
@@ -3115,11 +3129,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46112.60208333333</v>
       </c>
       <c r="B169" t="n">
-        <v>1.5829</v>
+        <v>1.6801</v>
       </c>
       <c r="C169" t="n">
         <v>168</v>
@@ -3131,11 +3145,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46112.60277777778</v>
       </c>
       <c r="B170" t="n">
-        <v>1.5857</v>
+        <v>1.6801</v>
       </c>
       <c r="C170" t="n">
         <v>169</v>
@@ -3147,11 +3161,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46112.60347222222</v>
       </c>
       <c r="B171" t="n">
-        <v>1.582</v>
+        <v>1.6801</v>
       </c>
       <c r="C171" t="n">
         <v>170</v>
@@ -3163,11 +3177,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46112.60416666666</v>
       </c>
       <c r="B172" t="n">
-        <v>1.5792</v>
+        <v>1.6801</v>
       </c>
       <c r="C172" t="n">
         <v>171</v>
@@ -3179,11 +3193,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46112.60486111111</v>
       </c>
       <c r="B173" t="n">
-        <v>1.5789</v>
+        <v>1.6801</v>
       </c>
       <c r="C173" t="n">
         <v>172</v>
@@ -3195,11 +3209,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46112.60555555556</v>
       </c>
       <c r="B174" t="n">
-        <v>1.5736</v>
+        <v>1.6801</v>
       </c>
       <c r="C174" t="n">
         <v>173</v>
@@ -3211,11 +3225,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46112.60625</v>
       </c>
       <c r="B175" t="n">
-        <v>1.5759</v>
+        <v>1.6801</v>
       </c>
       <c r="C175" t="n">
         <v>174</v>
@@ -3227,11 +3241,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46112.60694444444</v>
       </c>
       <c r="B176" t="n">
-        <v>1.5737</v>
+        <v>1.6801</v>
       </c>
       <c r="C176" t="n">
         <v>175</v>
@@ -3243,11 +3257,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46112.60763888889</v>
       </c>
       <c r="B177" t="n">
-        <v>1.5743</v>
+        <v>1.6801</v>
       </c>
       <c r="C177" t="n">
         <v>176</v>
@@ -3259,11 +3273,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46112.60833333333</v>
       </c>
       <c r="B178" t="n">
-        <v>1.5739</v>
+        <v>1.6801</v>
       </c>
       <c r="C178" t="n">
         <v>177</v>
@@ -3275,11 +3289,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46112.60902777778</v>
       </c>
       <c r="B179" t="n">
-        <v>1.5729</v>
+        <v>1.6801</v>
       </c>
       <c r="C179" t="n">
         <v>178</v>
@@ -3291,11 +3305,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46112.60972222222</v>
       </c>
       <c r="B180" t="n">
-        <v>1.5739</v>
+        <v>1.6801</v>
       </c>
       <c r="C180" t="n">
         <v>179</v>
@@ -3307,11 +3321,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46112.61041666667</v>
       </c>
       <c r="B181" t="n">
-        <v>1.5762</v>
+        <v>1.6801</v>
       </c>
       <c r="C181" t="n">
         <v>180</v>
